--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/15,09,26 ПОКОМ КИ/дв 15,09,26 лгрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/15,09,26 ПОКОМ КИ/дв 15,09,26 лгрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\09,26\15,09,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB77ADE-F810-41A0-BB2A-93793E3A3793}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27458B8A-FCC3-4EAC-BE02-315E97A2DEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AP$129</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -730,7 +722,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -745,10 +737,8 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -769,7 +759,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -6613,26 +6603,26 @@
   <dimension ref="A1:AV500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.140625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="3" style="14" customWidth="1"/>
-    <col min="3" max="4" width="6" style="14" customWidth="1"/>
-    <col min="5" max="6" width="7" style="14" customWidth="1"/>
+    <col min="1" max="1" width="41.42578125" customWidth="1"/>
+    <col min="2" max="2" width="3" customWidth="1"/>
+    <col min="3" max="4" width="6" customWidth="1"/>
+    <col min="5" max="6" width="7" customWidth="1"/>
     <col min="7" max="7" width="5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="5" style="14" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="14" customWidth="1"/>
-    <col min="10" max="10" width="1" style="14" customWidth="1"/>
-    <col min="11" max="12" width="7" style="14" customWidth="1"/>
-    <col min="13" max="14" width="0.42578125" style="14" customWidth="1"/>
-    <col min="15" max="26" width="7" style="14" customWidth="1"/>
-    <col min="27" max="28" width="7" style="17" customWidth="1"/>
-    <col min="29" max="30" width="5" style="14" customWidth="1"/>
-    <col min="31" max="32" width="6.85546875" style="14" customWidth="1"/>
-    <col min="33" max="36" width="6" style="14" customWidth="1"/>
-    <col min="37" max="39" width="6.85546875" style="14" customWidth="1"/>
-    <col min="40" max="40" width="6" style="14" customWidth="1"/>
-    <col min="41" max="41" width="11" style="14" customWidth="1"/>
-    <col min="42" max="43" width="7" style="14" customWidth="1"/>
-    <col min="44" max="48" width="8" style="14" customWidth="1"/>
+    <col min="8" max="8" width="5" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" customWidth="1"/>
+    <col min="10" max="10" width="1" customWidth="1"/>
+    <col min="11" max="12" width="7" customWidth="1"/>
+    <col min="13" max="14" width="0.42578125" customWidth="1"/>
+    <col min="15" max="26" width="7" customWidth="1"/>
+    <col min="27" max="28" width="7" style="15" customWidth="1"/>
+    <col min="29" max="30" width="5" customWidth="1"/>
+    <col min="31" max="32" width="6.85546875" customWidth="1"/>
+    <col min="33" max="36" width="6" customWidth="1"/>
+    <col min="37" max="39" width="6.85546875" customWidth="1"/>
+    <col min="40" max="40" width="6" customWidth="1"/>
+    <col min="41" max="41" width="11" customWidth="1"/>
+    <col min="42" max="43" width="7" customWidth="1"/>
+    <col min="44" max="48" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">
@@ -6659,11 +6649,11 @@
       <c r="U1" s="12"/>
       <c r="V1" s="12"/>
       <c r="W1" s="12"/>
-      <c r="X1" s="18">
+      <c r="X1" s="16">
         <v>1.865</v>
       </c>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18">
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16">
         <v>0.437</v>
       </c>
       <c r="AA1" s="12"/>
@@ -7113,7 +7103,10 @@
         <f>SUM(AQ6:AQ500)</f>
         <v>9650</v>
       </c>
-      <c r="AR5" s="12"/>
+      <c r="AR5" s="3">
+        <f>SUM(AR6:AR500)</f>
+        <v>8931.263399999998</v>
+      </c>
       <c r="AS5" s="12"/>
       <c r="AT5" s="12"/>
       <c r="AU5" s="12"/>
@@ -7190,8 +7183,8 @@
         <f>X6*$Z$1</f>
         <v>1193.7542234982</v>
       </c>
-      <c r="AA6" s="16"/>
-      <c r="AB6" s="16"/>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="12"/>
       <c r="AC6" s="12">
         <f>(F6+O6+P6+Q6+R6+S6+T6+U6+Y6+Z6)/V6</f>
         <v>11.864999999999998</v>
@@ -7239,7 +7232,10 @@
         <f>ROUND(G6*Z6,0)</f>
         <v>1194</v>
       </c>
-      <c r="AR6" s="12"/>
+      <c r="AR6" s="12">
+        <f>V6*G6</f>
+        <v>683.02780000000007</v>
+      </c>
       <c r="AS6" s="12"/>
       <c r="AT6" s="12"/>
       <c r="AU6" s="12"/>
@@ -7310,8 +7306,8 @@
         <v>0</v>
       </c>
       <c r="Z7" s="4"/>
-      <c r="AA7" s="16"/>
-      <c r="AB7" s="16"/>
+      <c r="AA7" s="12"/>
+      <c r="AB7" s="12"/>
       <c r="AC7" s="12">
         <f t="shared" ref="AC7:AC70" si="8">(F7+O7+P7+Q7+R7+S7+T7+U7+Y7+Z7)/V7</f>
         <v>12.274502791938108</v>
@@ -7352,14 +7348,17 @@
       </c>
       <c r="AO7" s="12"/>
       <c r="AP7" s="12">
-        <f t="shared" ref="AP7:AQ70" si="9">ROUND(G7*Y7,0)</f>
+        <f t="shared" ref="AP7:AP70" si="9">ROUND(G7*Y7,0)</f>
         <v>0</v>
       </c>
       <c r="AQ7" s="12">
         <f t="shared" ref="AQ7:AQ70" si="10">ROUND(G7*Z7,0)</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="12"/>
+      <c r="AR7" s="12">
+        <f t="shared" ref="AR7:AR70" si="11">V7*G7</f>
+        <v>230.37759999999997</v>
+      </c>
       <c r="AS7" s="12"/>
       <c r="AT7" s="12"/>
       <c r="AU7" s="12"/>
@@ -7433,8 +7432,8 @@
         <f>X8*$Z$1</f>
         <v>219.81516155099999</v>
       </c>
-      <c r="AA8" s="16"/>
-      <c r="AB8" s="16"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="12"/>
       <c r="AC8" s="12">
         <f t="shared" si="8"/>
         <v>12.882441980318136</v>
@@ -7482,7 +7481,10 @@
         <f t="shared" si="10"/>
         <v>220</v>
       </c>
-      <c r="AR8" s="12"/>
+      <c r="AR8" s="12">
+        <f t="shared" si="11"/>
+        <v>269.71019999999999</v>
+      </c>
       <c r="AS8" s="12"/>
       <c r="AT8" s="12"/>
       <c r="AU8" s="12"/>
@@ -7537,8 +7539,8 @@
         <v>0</v>
       </c>
       <c r="Z9" s="4"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
+      <c r="AA9" s="12"/>
+      <c r="AB9" s="12"/>
       <c r="AC9" s="12" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
@@ -7588,7 +7590,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR9" s="12"/>
+      <c r="AR9" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AS9" s="12"/>
       <c r="AT9" s="12"/>
       <c r="AU9" s="12"/>
@@ -7654,7 +7659,7 @@
         <v>518.84315200000037</v>
       </c>
       <c r="X10" s="4">
-        <f t="shared" ref="X10:X11" si="11">W10+V10*$X$1</f>
+        <f t="shared" ref="X10:X11" si="12">W10+V10*$X$1</f>
         <v>829.17915200000039</v>
       </c>
       <c r="Y10" s="4">
@@ -7662,11 +7667,11 @@
         <v>466.8278625760002</v>
       </c>
       <c r="Z10" s="4">
-        <f t="shared" ref="Z10:Z11" si="12">X10*$Z$1</f>
+        <f t="shared" ref="Z10:Z11" si="13">X10*$Z$1</f>
         <v>362.35128942400019</v>
       </c>
-      <c r="AA10" s="16"/>
-      <c r="AB10" s="16"/>
+      <c r="AA10" s="12"/>
+      <c r="AB10" s="12"/>
       <c r="AC10" s="12">
         <f t="shared" si="8"/>
         <v>12.865000000000002</v>
@@ -7714,7 +7719,10 @@
         <f t="shared" si="10"/>
         <v>163</v>
       </c>
-      <c r="AR10" s="12"/>
+      <c r="AR10" s="12">
+        <f t="shared" si="11"/>
+        <v>74.88000000000001</v>
+      </c>
       <c r="AS10" s="12"/>
       <c r="AT10" s="12"/>
       <c r="AU10" s="12"/>
@@ -7780,7 +7788,7 @@
         <v>88.936000000000149</v>
       </c>
       <c r="X11" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>472.00700000000018</v>
       </c>
       <c r="Y11" s="4">
@@ -7788,11 +7796,11 @@
         <v>265.7399410000001</v>
       </c>
       <c r="Z11" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>206.26705900000007</v>
       </c>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
+      <c r="AA11" s="12"/>
+      <c r="AB11" s="12"/>
       <c r="AC11" s="12">
         <f t="shared" si="8"/>
         <v>12.865000000000002</v>
@@ -7842,7 +7850,10 @@
         <f t="shared" si="10"/>
         <v>93</v>
       </c>
-      <c r="AR11" s="12"/>
+      <c r="AR11" s="12">
+        <f t="shared" si="11"/>
+        <v>92.43</v>
+      </c>
       <c r="AS11" s="12"/>
       <c r="AT11" s="12"/>
       <c r="AU11" s="12"/>
@@ -7909,8 +7920,8 @@
         <v>0</v>
       </c>
       <c r="Z12" s="4"/>
-      <c r="AA12" s="16"/>
-      <c r="AB12" s="16"/>
+      <c r="AA12" s="12"/>
+      <c r="AB12" s="12"/>
       <c r="AC12" s="12">
         <f t="shared" si="8"/>
         <v>10.955882352941178</v>
@@ -7958,7 +7969,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR12" s="12"/>
+      <c r="AR12" s="12">
+        <f t="shared" si="11"/>
+        <v>3.468</v>
+      </c>
       <c r="AS12" s="12"/>
       <c r="AT12" s="12"/>
       <c r="AU12" s="12"/>
@@ -8027,11 +8041,11 @@
         <v>100</v>
       </c>
       <c r="Z13" s="4"/>
-      <c r="AA13" s="16">
+      <c r="AA13" s="12">
         <f>VLOOKUP(A13,[1]Sheet!$A:$Y,24,0)</f>
         <v>100</v>
       </c>
-      <c r="AB13" s="16">
+      <c r="AB13" s="12">
         <f>VLOOKUP(A13,[1]Sheet!$A:$Y,25,0)</f>
         <v>0</v>
       </c>
@@ -8082,7 +8096,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR13" s="12"/>
+      <c r="AR13" s="12">
+        <f t="shared" si="11"/>
+        <v>3.24</v>
+      </c>
       <c r="AS13" s="12"/>
       <c r="AT13" s="12"/>
       <c r="AU13" s="12"/>
@@ -8155,8 +8172,8 @@
         <f>X14*$Z$1</f>
         <v>115.46108099999998</v>
       </c>
-      <c r="AA14" s="16"/>
-      <c r="AB14" s="16"/>
+      <c r="AA14" s="12"/>
+      <c r="AB14" s="12"/>
       <c r="AC14" s="12">
         <f t="shared" si="8"/>
         <v>12.864999999999997</v>
@@ -8204,7 +8221,10 @@
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="AR14" s="12"/>
+      <c r="AR14" s="12">
+        <f t="shared" si="11"/>
+        <v>9.6220000000000017</v>
+      </c>
       <c r="AS14" s="12"/>
       <c r="AT14" s="12"/>
       <c r="AU14" s="12"/>
@@ -8276,8 +8296,8 @@
         <v>37.917945999999802</v>
       </c>
       <c r="Z15" s="4"/>
-      <c r="AA15" s="16"/>
-      <c r="AB15" s="16"/>
+      <c r="AA15" s="12"/>
+      <c r="AB15" s="12"/>
       <c r="AC15" s="12">
         <f t="shared" si="8"/>
         <v>11</v>
@@ -8325,7 +8345,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR15" s="12"/>
+      <c r="AR15" s="12">
+        <f t="shared" si="11"/>
+        <v>233.12559999999999</v>
+      </c>
       <c r="AS15" s="12"/>
       <c r="AT15" s="12"/>
       <c r="AU15" s="12"/>
@@ -8404,8 +8427,8 @@
         <f>X16*$Z$1</f>
         <v>710.49944301300104</v>
       </c>
-      <c r="AA16" s="16"/>
-      <c r="AB16" s="16"/>
+      <c r="AA16" s="12"/>
+      <c r="AB16" s="12"/>
       <c r="AC16" s="12">
         <f t="shared" si="8"/>
         <v>11.865</v>
@@ -8453,7 +8476,10 @@
         <f t="shared" si="10"/>
         <v>710</v>
       </c>
-      <c r="AR16" s="12"/>
+      <c r="AR16" s="12">
+        <f t="shared" si="11"/>
+        <v>816.20259999999996</v>
+      </c>
       <c r="AS16" s="12"/>
       <c r="AT16" s="12"/>
       <c r="AU16" s="12"/>
@@ -8523,8 +8549,8 @@
         <v>16.45969999999997</v>
       </c>
       <c r="Z17" s="4"/>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
+      <c r="AA17" s="12"/>
+      <c r="AB17" s="12"/>
       <c r="AC17" s="12">
         <f t="shared" si="8"/>
         <v>11</v>
@@ -8572,7 +8598,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR17" s="12"/>
+      <c r="AR17" s="12">
+        <f t="shared" si="11"/>
+        <v>19.036799999999999</v>
+      </c>
       <c r="AS17" s="12"/>
       <c r="AT17" s="12"/>
       <c r="AU17" s="12"/>
@@ -8641,8 +8670,8 @@
         <v>0</v>
       </c>
       <c r="Z18" s="4"/>
-      <c r="AA18" s="16"/>
-      <c r="AB18" s="16"/>
+      <c r="AA18" s="12"/>
+      <c r="AB18" s="12"/>
       <c r="AC18" s="12">
         <f t="shared" si="8"/>
         <v>15.530308383741307</v>
@@ -8690,7 +8719,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR18" s="12"/>
+      <c r="AR18" s="12">
+        <f t="shared" si="11"/>
+        <v>14.151199999999999</v>
+      </c>
       <c r="AS18" s="12"/>
       <c r="AT18" s="12"/>
       <c r="AU18" s="12"/>
@@ -8760,8 +8792,8 @@
         <v>9.1872000000000043</v>
       </c>
       <c r="Z19" s="4"/>
-      <c r="AA19" s="16"/>
-      <c r="AB19" s="16"/>
+      <c r="AA19" s="12"/>
+      <c r="AB19" s="12"/>
       <c r="AC19" s="12">
         <f t="shared" si="8"/>
         <v>11</v>
@@ -8809,7 +8841,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR19" s="12"/>
+      <c r="AR19" s="12">
+        <f t="shared" si="11"/>
+        <v>2.5902000000000003</v>
+      </c>
       <c r="AS19" s="12"/>
       <c r="AT19" s="12"/>
       <c r="AU19" s="12"/>
@@ -8875,7 +8910,7 @@
         <v>53.671262858799309</v>
       </c>
       <c r="X20" s="4">
-        <f t="shared" ref="X20:X21" si="13">W20+V20*$X$1</f>
+        <f t="shared" ref="X20:X21" si="14">W20+V20*$X$1</f>
         <v>562.20267785879923</v>
       </c>
       <c r="Y20" s="4">
@@ -8886,8 +8921,8 @@
         <f>X20*$Z$1</f>
         <v>245.68257022429526</v>
       </c>
-      <c r="AA20" s="16"/>
-      <c r="AB20" s="16"/>
+      <c r="AA20" s="12"/>
+      <c r="AB20" s="12"/>
       <c r="AC20" s="12">
         <f t="shared" si="8"/>
         <v>12.864999999999998</v>
@@ -8935,7 +8970,10 @@
         <f t="shared" si="10"/>
         <v>246</v>
       </c>
-      <c r="AR20" s="12"/>
+      <c r="AR20" s="12">
+        <f t="shared" si="11"/>
+        <v>272.67099999999999</v>
+      </c>
       <c r="AS20" s="12"/>
       <c r="AT20" s="12"/>
       <c r="AU20" s="12"/>
@@ -8997,7 +9035,7 @@
         <v>47.549900000000093</v>
       </c>
       <c r="X21" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>133.77817500000009</v>
       </c>
       <c r="Y21" s="4">
@@ -9005,8 +9043,8 @@
         <v>133.77817500000009</v>
       </c>
       <c r="Z21" s="4"/>
-      <c r="AA21" s="16"/>
-      <c r="AB21" s="16"/>
+      <c r="AA21" s="12"/>
+      <c r="AB21" s="12"/>
       <c r="AC21" s="12">
         <f t="shared" si="8"/>
         <v>12.865</v>
@@ -9054,7 +9092,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR21" s="12"/>
+      <c r="AR21" s="12">
+        <f t="shared" si="11"/>
+        <v>46.234999999999999</v>
+      </c>
       <c r="AS21" s="12"/>
       <c r="AT21" s="12"/>
       <c r="AU21" s="12"/>
@@ -9125,8 +9166,8 @@
         <v>0</v>
       </c>
       <c r="Z22" s="4"/>
-      <c r="AA22" s="16"/>
-      <c r="AB22" s="16"/>
+      <c r="AA22" s="12"/>
+      <c r="AB22" s="12"/>
       <c r="AC22" s="12">
         <f t="shared" si="8"/>
         <v>17.368010847935039</v>
@@ -9176,7 +9217,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR22" s="12"/>
+      <c r="AR22" s="12">
+        <f t="shared" si="11"/>
+        <v>89.749800000000008</v>
+      </c>
       <c r="AS22" s="12"/>
       <c r="AT22" s="12"/>
       <c r="AU22" s="12"/>
@@ -9231,8 +9275,8 @@
         <v>0</v>
       </c>
       <c r="Z23" s="4"/>
-      <c r="AA23" s="16"/>
-      <c r="AB23" s="16"/>
+      <c r="AA23" s="12"/>
+      <c r="AB23" s="12"/>
       <c r="AC23" s="12" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
@@ -9282,7 +9326,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR23" s="12"/>
+      <c r="AR23" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AS23" s="12"/>
       <c r="AT23" s="12"/>
       <c r="AU23" s="12"/>
@@ -9349,12 +9396,12 @@
         <v>0</v>
       </c>
       <c r="Y24" s="4">
-        <f t="shared" ref="Y24:Y29" si="14">X24</f>
+        <f t="shared" ref="Y24:Y29" si="15">X24</f>
         <v>0</v>
       </c>
       <c r="Z24" s="4"/>
-      <c r="AA24" s="16"/>
-      <c r="AB24" s="16"/>
+      <c r="AA24" s="12"/>
+      <c r="AB24" s="12"/>
       <c r="AC24" s="12">
         <f t="shared" si="8"/>
         <v>12.796145055581137</v>
@@ -9404,7 +9451,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR24" s="12"/>
+      <c r="AR24" s="12">
+        <f t="shared" si="11"/>
+        <v>140.28140000000002</v>
+      </c>
       <c r="AS24" s="12"/>
       <c r="AT24" s="12"/>
       <c r="AU24" s="12"/>
@@ -9470,15 +9520,15 @@
         <v>168.708</v>
       </c>
       <c r="Y25" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>168.708</v>
       </c>
       <c r="Z25" s="4">
         <f>0.5*X25</f>
         <v>84.353999999999999</v>
       </c>
-      <c r="AA25" s="16"/>
-      <c r="AB25" s="16"/>
+      <c r="AA25" s="12"/>
+      <c r="AB25" s="12"/>
       <c r="AC25" s="12">
         <f t="shared" si="8"/>
         <v>13.793826383598846</v>
@@ -9526,7 +9576,10 @@
         <f t="shared" si="10"/>
         <v>84</v>
       </c>
-      <c r="AR25" s="12"/>
+      <c r="AR25" s="12">
+        <f t="shared" si="11"/>
+        <v>30.193000000000001</v>
+      </c>
       <c r="AS25" s="12"/>
       <c r="AT25" s="12"/>
       <c r="AU25" s="12"/>
@@ -9596,12 +9649,12 @@
         <v>84.296299999999974</v>
       </c>
       <c r="Y26" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>84.296299999999974</v>
       </c>
       <c r="Z26" s="4"/>
-      <c r="AA26" s="16"/>
-      <c r="AB26" s="16"/>
+      <c r="AA26" s="12"/>
+      <c r="AB26" s="12"/>
       <c r="AC26" s="12">
         <f t="shared" si="8"/>
         <v>11</v>
@@ -9649,7 +9702,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR26" s="12"/>
+      <c r="AR26" s="12">
+        <f t="shared" si="11"/>
+        <v>33.269799999999996</v>
+      </c>
       <c r="AS26" s="12"/>
       <c r="AT26" s="12"/>
       <c r="AU26" s="12"/>
@@ -9714,12 +9770,12 @@
         <v>20</v>
       </c>
       <c r="Y27" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="Z27" s="4"/>
-      <c r="AA27" s="16"/>
-      <c r="AB27" s="16"/>
+      <c r="AA27" s="12"/>
+      <c r="AB27" s="12"/>
       <c r="AC27" s="12">
         <f t="shared" si="8"/>
         <v>16.000730556631343</v>
@@ -9767,7 +9823,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR27" s="12"/>
+      <c r="AR27" s="12">
+        <f t="shared" si="11"/>
+        <v>22.7224</v>
+      </c>
       <c r="AS27" s="12"/>
       <c r="AT27" s="12"/>
       <c r="AU27" s="12"/>
@@ -9835,15 +9894,15 @@
         <v>1004.9707999999998</v>
       </c>
       <c r="Y28" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1004.9707999999998</v>
       </c>
       <c r="Z28" s="4">
-        <f t="shared" ref="Z28:Z29" si="15">0.5*X28</f>
+        <f t="shared" ref="Z28:Z29" si="16">0.5*X28</f>
         <v>502.48539999999991</v>
       </c>
-      <c r="AA28" s="16"/>
-      <c r="AB28" s="16"/>
+      <c r="AA28" s="12"/>
+      <c r="AB28" s="12"/>
       <c r="AC28" s="12">
         <f t="shared" si="8"/>
         <v>11.585354495564982</v>
@@ -9893,7 +9952,10 @@
         <f t="shared" si="10"/>
         <v>502</v>
       </c>
-      <c r="AR28" s="12"/>
+      <c r="AR28" s="12">
+        <f t="shared" si="11"/>
+        <v>316.95459999999997</v>
+      </c>
       <c r="AS28" s="12"/>
       <c r="AT28" s="12"/>
       <c r="AU28" s="12"/>
@@ -9963,15 +10025,15 @@
         <v>687.42699999999945</v>
       </c>
       <c r="Y29" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>687.42699999999945</v>
       </c>
       <c r="Z29" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>343.71349999999973</v>
       </c>
-      <c r="AA29" s="16"/>
-      <c r="AB29" s="16"/>
+      <c r="AA29" s="12"/>
+      <c r="AB29" s="12"/>
       <c r="AC29" s="12">
         <f t="shared" si="8"/>
         <v>11.901073275850768</v>
@@ -10021,7 +10083,10 @@
         <f t="shared" si="10"/>
         <v>344</v>
       </c>
-      <c r="AR29" s="12"/>
+      <c r="AR29" s="12">
+        <f t="shared" si="11"/>
+        <v>381.44899999999996</v>
+      </c>
       <c r="AS29" s="12"/>
       <c r="AT29" s="12"/>
       <c r="AU29" s="12"/>
@@ -10076,8 +10141,8 @@
         <v>0</v>
       </c>
       <c r="Z30" s="4"/>
-      <c r="AA30" s="16"/>
-      <c r="AB30" s="16"/>
+      <c r="AA30" s="12"/>
+      <c r="AB30" s="12"/>
       <c r="AC30" s="12" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
@@ -10127,7 +10192,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR30" s="12"/>
+      <c r="AR30" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AS30" s="12"/>
       <c r="AT30" s="12"/>
       <c r="AU30" s="12"/>
@@ -10197,8 +10265,8 @@
         <v>104.24671499999984</v>
       </c>
       <c r="Z31" s="4"/>
-      <c r="AA31" s="16"/>
-      <c r="AB31" s="16"/>
+      <c r="AA31" s="12"/>
+      <c r="AB31" s="12"/>
       <c r="AC31" s="12">
         <f t="shared" si="8"/>
         <v>12.865</v>
@@ -10246,7 +10314,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR31" s="12"/>
+      <c r="AR31" s="12">
+        <f t="shared" si="11"/>
+        <v>37.150999999999996</v>
+      </c>
       <c r="AS31" s="12"/>
       <c r="AT31" s="12"/>
       <c r="AU31" s="12"/>
@@ -10301,8 +10372,8 @@
         <v>0</v>
       </c>
       <c r="Z32" s="4"/>
-      <c r="AA32" s="16"/>
-      <c r="AB32" s="16"/>
+      <c r="AA32" s="12"/>
+      <c r="AB32" s="12"/>
       <c r="AC32" s="12" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
@@ -10352,7 +10423,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR32" s="12"/>
+      <c r="AR32" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AS32" s="12"/>
       <c r="AT32" s="12"/>
       <c r="AU32" s="12"/>
@@ -10407,8 +10481,8 @@
         <v>0</v>
       </c>
       <c r="Z33" s="4"/>
-      <c r="AA33" s="16"/>
-      <c r="AB33" s="16"/>
+      <c r="AA33" s="12"/>
+      <c r="AB33" s="12"/>
       <c r="AC33" s="12" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
@@ -10458,7 +10532,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR33" s="12"/>
+      <c r="AR33" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AS33" s="12"/>
       <c r="AT33" s="12"/>
       <c r="AU33" s="12"/>
@@ -10534,8 +10611,8 @@
         <f>0.5*X34</f>
         <v>2000</v>
       </c>
-      <c r="AA34" s="16"/>
-      <c r="AB34" s="16"/>
+      <c r="AA34" s="12"/>
+      <c r="AB34" s="12"/>
       <c r="AC34" s="12">
         <f t="shared" si="8"/>
         <v>11.614973262032086</v>
@@ -10583,7 +10660,10 @@
         <f t="shared" si="10"/>
         <v>800</v>
       </c>
-      <c r="AR34" s="12"/>
+      <c r="AR34" s="12">
+        <f t="shared" si="11"/>
+        <v>448.8</v>
+      </c>
       <c r="AS34" s="12"/>
       <c r="AT34" s="12"/>
       <c r="AU34" s="12"/>
@@ -10660,8 +10740,8 @@
         <f>X35*$Z$1</f>
         <v>174.10822899999991</v>
       </c>
-      <c r="AA35" s="16"/>
-      <c r="AB35" s="16"/>
+      <c r="AA35" s="12"/>
+      <c r="AB35" s="12"/>
       <c r="AC35" s="12">
         <f t="shared" si="8"/>
         <v>12.865</v>
@@ -10709,7 +10789,10 @@
         <f t="shared" si="10"/>
         <v>78</v>
       </c>
-      <c r="AR35" s="12"/>
+      <c r="AR35" s="12">
+        <f t="shared" si="11"/>
+        <v>56.61</v>
+      </c>
       <c r="AS35" s="12"/>
       <c r="AT35" s="12"/>
       <c r="AU35" s="12"/>
@@ -10778,15 +10861,15 @@
         <v>600</v>
       </c>
       <c r="Y36" s="4">
-        <f t="shared" ref="Y36:Y38" si="16">X36</f>
+        <f t="shared" ref="Y36:Y38" si="17">X36</f>
         <v>600</v>
       </c>
       <c r="Z36" s="4">
         <f>0.5*X36</f>
         <v>300</v>
       </c>
-      <c r="AA36" s="16"/>
-      <c r="AB36" s="16"/>
+      <c r="AA36" s="12"/>
+      <c r="AB36" s="12"/>
       <c r="AC36" s="12">
         <f t="shared" si="8"/>
         <v>12.964362850971924</v>
@@ -10834,7 +10917,10 @@
         <f t="shared" si="10"/>
         <v>120</v>
       </c>
-      <c r="AR36" s="12"/>
+      <c r="AR36" s="12">
+        <f t="shared" si="11"/>
+        <v>74.08</v>
+      </c>
       <c r="AS36" s="12"/>
       <c r="AT36" s="12"/>
       <c r="AU36" s="12"/>
@@ -10899,12 +10985,12 @@
         <v>30</v>
       </c>
       <c r="Y37" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>30</v>
       </c>
       <c r="Z37" s="4"/>
-      <c r="AA37" s="16"/>
-      <c r="AB37" s="16"/>
+      <c r="AA37" s="12"/>
+      <c r="AB37" s="12"/>
       <c r="AC37" s="12">
         <f t="shared" si="8"/>
         <v>10.357142857142858</v>
@@ -10952,7 +11038,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR37" s="12"/>
+      <c r="AR37" s="12">
+        <f t="shared" si="11"/>
+        <v>1.1199999999999999</v>
+      </c>
       <c r="AS37" s="12"/>
       <c r="AT37" s="12"/>
       <c r="AU37" s="12"/>
@@ -10991,7 +11080,7 @@
         <v>159.05000000000001</v>
       </c>
       <c r="L38" s="12">
-        <f t="shared" ref="L38:L69" si="17">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="18">E38-K38</f>
         <v>8.8649999999999807</v>
       </c>
       <c r="M38" s="12"/>
@@ -11010,7 +11099,7 @@
         <v>20</v>
       </c>
       <c r="V38" s="12">
-        <f t="shared" ref="V38:V69" si="18">E38/5</f>
+        <f t="shared" ref="V38:V69" si="19">E38/5</f>
         <v>33.582999999999998</v>
       </c>
       <c r="W38" s="4">
@@ -11021,18 +11110,18 @@
         <v>20</v>
       </c>
       <c r="Y38" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="Z38" s="4"/>
-      <c r="AA38" s="16"/>
-      <c r="AB38" s="16"/>
+      <c r="AA38" s="12"/>
+      <c r="AB38" s="12"/>
       <c r="AC38" s="12">
         <f t="shared" si="8"/>
         <v>11.78796117083048</v>
       </c>
       <c r="AD38" s="12">
-        <f t="shared" ref="AD38:AD69" si="19">(F38+O38+P38+Q38+R38+S38+T38+U38)/V38</f>
+        <f t="shared" ref="AD38:AD69" si="20">(F38+O38+P38+Q38+R38+S38+T38+U38)/V38</f>
         <v>11.192421761010035</v>
       </c>
       <c r="AE38" s="12">
@@ -11074,7 +11163,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR38" s="12"/>
+      <c r="AR38" s="12">
+        <f t="shared" si="11"/>
+        <v>33.582999999999998</v>
+      </c>
       <c r="AS38" s="12"/>
       <c r="AT38" s="12"/>
       <c r="AU38" s="12"/>
@@ -11111,7 +11203,7 @@
         <v>493</v>
       </c>
       <c r="L39" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M39" s="12"/>
@@ -11128,7 +11220,7 @@
         <v>183.6</v>
       </c>
       <c r="V39" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>98.6</v>
       </c>
       <c r="W39" s="4">
@@ -11147,14 +11239,14 @@
         <f>X39*$Z$1</f>
         <v>234.00869299999997</v>
       </c>
-      <c r="AA39" s="16"/>
-      <c r="AB39" s="16"/>
+      <c r="AA39" s="12"/>
+      <c r="AB39" s="12"/>
       <c r="AC39" s="12">
         <f t="shared" si="8"/>
         <v>12.864999999999998</v>
       </c>
       <c r="AD39" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.4340770791075057</v>
       </c>
       <c r="AE39" s="12">
@@ -11196,7 +11288,10 @@
         <f t="shared" si="10"/>
         <v>23</v>
       </c>
-      <c r="AR39" s="12"/>
+      <c r="AR39" s="12">
+        <f t="shared" si="11"/>
+        <v>9.86</v>
+      </c>
       <c r="AS39" s="12"/>
       <c r="AT39" s="12"/>
       <c r="AU39" s="12"/>
@@ -11233,7 +11328,7 @@
         <v>410</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-290</v>
       </c>
       <c r="M40" s="12"/>
@@ -11248,7 +11343,7 @@
       <c r="T40" s="12"/>
       <c r="U40" s="12"/>
       <c r="V40" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>24</v>
       </c>
       <c r="W40" s="4">
@@ -11259,21 +11354,21 @@
         <v>250</v>
       </c>
       <c r="Y40" s="4">
-        <f t="shared" ref="Y40:Y46" si="20">X40</f>
+        <f t="shared" ref="Y40:Y46" si="21">X40</f>
         <v>250</v>
       </c>
       <c r="Z40" s="4">
         <f>0.5*X40</f>
         <v>125</v>
       </c>
-      <c r="AA40" s="16"/>
-      <c r="AB40" s="16"/>
+      <c r="AA40" s="12"/>
+      <c r="AB40" s="12"/>
       <c r="AC40" s="12">
         <f t="shared" si="8"/>
         <v>16.375</v>
       </c>
       <c r="AD40" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.75</v>
       </c>
       <c r="AE40" s="12">
@@ -11315,7 +11410,10 @@
         <f t="shared" si="10"/>
         <v>44</v>
       </c>
-      <c r="AR40" s="12"/>
+      <c r="AR40" s="12">
+        <f t="shared" si="11"/>
+        <v>8.3999999999999986</v>
+      </c>
       <c r="AS40" s="12"/>
       <c r="AT40" s="12"/>
       <c r="AU40" s="12"/>
@@ -11354,7 +11452,7 @@
         <v>105.9</v>
       </c>
       <c r="L41" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-37.975999999999999</v>
       </c>
       <c r="M41" s="12"/>
@@ -11371,7 +11469,7 @@
         <v>20</v>
       </c>
       <c r="V41" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.584800000000001</v>
       </c>
       <c r="W41" s="4">
@@ -11382,18 +11480,18 @@
         <v>30</v>
       </c>
       <c r="Y41" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>30</v>
       </c>
       <c r="Z41" s="4"/>
-      <c r="AA41" s="16"/>
-      <c r="AB41" s="16"/>
+      <c r="AA41" s="12"/>
+      <c r="AB41" s="12"/>
       <c r="AC41" s="12">
         <f t="shared" si="8"/>
         <v>12.567207467169188</v>
       </c>
       <c r="AD41" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.358856957776338</v>
       </c>
       <c r="AE41" s="12">
@@ -11435,7 +11533,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR41" s="12"/>
+      <c r="AR41" s="12">
+        <f t="shared" si="11"/>
+        <v>13.584800000000001</v>
+      </c>
       <c r="AS41" s="12"/>
       <c r="AT41" s="12"/>
       <c r="AU41" s="12"/>
@@ -11474,7 +11575,7 @@
         <v>770</v>
       </c>
       <c r="L42" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-270</v>
       </c>
       <c r="M42" s="12"/>
@@ -11493,7 +11594,7 @@
         <v>150</v>
       </c>
       <c r="V42" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>100</v>
       </c>
       <c r="W42" s="4">
@@ -11505,21 +11606,21 @@
         <v>592</v>
       </c>
       <c r="Y42" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>592</v>
       </c>
       <c r="Z42" s="4">
-        <f t="shared" ref="Z42:Z43" si="21">0.5*X42</f>
+        <f t="shared" ref="Z42:Z43" si="22">0.5*X42</f>
         <v>296</v>
       </c>
-      <c r="AA42" s="16"/>
-      <c r="AB42" s="16"/>
+      <c r="AA42" s="12"/>
+      <c r="AB42" s="12"/>
       <c r="AC42" s="12">
         <f t="shared" si="8"/>
         <v>13.96</v>
       </c>
       <c r="AD42" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.08</v>
       </c>
       <c r="AE42" s="12">
@@ -11561,7 +11662,10 @@
         <f t="shared" si="10"/>
         <v>118</v>
       </c>
-      <c r="AR42" s="12"/>
+      <c r="AR42" s="12">
+        <f t="shared" si="11"/>
+        <v>40</v>
+      </c>
       <c r="AS42" s="12"/>
       <c r="AT42" s="12"/>
       <c r="AU42" s="12"/>
@@ -11600,7 +11704,7 @@
         <v>431</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-216</v>
       </c>
       <c r="M43" s="12"/>
@@ -11621,7 +11725,7 @@
         <v>100</v>
       </c>
       <c r="V43" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>43</v>
       </c>
       <c r="W43" s="4">
@@ -11632,21 +11736,21 @@
         <v>150</v>
       </c>
       <c r="Y43" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>150</v>
       </c>
       <c r="Z43" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>75</v>
       </c>
-      <c r="AA43" s="16"/>
-      <c r="AB43" s="16"/>
+      <c r="AA43" s="12"/>
+      <c r="AB43" s="12"/>
       <c r="AC43" s="12">
         <f t="shared" si="8"/>
         <v>14.220930232558139</v>
       </c>
       <c r="AD43" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.9883720930232567</v>
       </c>
       <c r="AE43" s="12">
@@ -11688,7 +11792,10 @@
         <f t="shared" si="10"/>
         <v>30</v>
       </c>
-      <c r="AR43" s="12"/>
+      <c r="AR43" s="12">
+        <f t="shared" si="11"/>
+        <v>17.2</v>
+      </c>
       <c r="AS43" s="12"/>
       <c r="AT43" s="12"/>
       <c r="AU43" s="12"/>
@@ -11727,7 +11834,7 @@
         <v>291.05</v>
       </c>
       <c r="L44" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-120.45100000000002</v>
       </c>
       <c r="M44" s="12"/>
@@ -11742,7 +11849,7 @@
       <c r="T44" s="12"/>
       <c r="U44" s="12"/>
       <c r="V44" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>34.119799999999998</v>
       </c>
       <c r="W44" s="4">
@@ -11754,15 +11861,15 @@
         <v>250</v>
       </c>
       <c r="Y44" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>250</v>
       </c>
       <c r="Z44" s="4"/>
-      <c r="AA44" s="16">
+      <c r="AA44" s="12">
         <f>VLOOKUP(A44,[1]Sheet!$A:$Y,24,0)</f>
         <v>250</v>
       </c>
-      <c r="AB44" s="16" t="str">
+      <c r="AB44" s="12" t="str">
         <f>VLOOKUP(A44,[1]Sheet!$A:$Y,25,0)</f>
         <v>промо жц</v>
       </c>
@@ -11771,7 +11878,7 @@
         <v>12.104027573432434</v>
       </c>
       <c r="AD44" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.7769037333161393</v>
       </c>
       <c r="AE44" s="12">
@@ -11813,7 +11920,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR44" s="12"/>
+      <c r="AR44" s="12">
+        <f t="shared" si="11"/>
+        <v>34.119799999999998</v>
+      </c>
       <c r="AS44" s="12"/>
       <c r="AT44" s="12"/>
       <c r="AU44" s="12"/>
@@ -11852,7 +11962,7 @@
         <v>1498</v>
       </c>
       <c r="L45" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-148</v>
       </c>
       <c r="M45" s="12"/>
@@ -11873,7 +11983,7 @@
         <v>500</v>
       </c>
       <c r="V45" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>270</v>
       </c>
       <c r="W45" s="4">
@@ -11885,21 +11995,21 @@
         <v>1259</v>
       </c>
       <c r="Y45" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1259</v>
       </c>
       <c r="Z45" s="4">
-        <f t="shared" ref="Z45:Z46" si="22">0.5*X45</f>
+        <f t="shared" ref="Z45:Z46" si="23">0.5*X45</f>
         <v>629.5</v>
       </c>
-      <c r="AA45" s="16"/>
-      <c r="AB45" s="16"/>
+      <c r="AA45" s="12"/>
+      <c r="AB45" s="12"/>
       <c r="AC45" s="12">
         <f t="shared" si="8"/>
         <v>13.331481481481481</v>
       </c>
       <c r="AD45" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.337037037037037</v>
       </c>
       <c r="AE45" s="12">
@@ -11941,7 +12051,10 @@
         <f t="shared" si="10"/>
         <v>220</v>
       </c>
-      <c r="AR45" s="12"/>
+      <c r="AR45" s="12">
+        <f t="shared" si="11"/>
+        <v>94.5</v>
+      </c>
       <c r="AS45" s="12"/>
       <c r="AT45" s="12"/>
       <c r="AU45" s="12"/>
@@ -11980,7 +12093,7 @@
         <v>792</v>
       </c>
       <c r="L46" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-24</v>
       </c>
       <c r="M46" s="12"/>
@@ -11999,7 +12112,7 @@
         <v>400</v>
       </c>
       <c r="V46" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>153.6</v>
       </c>
       <c r="W46" s="4">
@@ -12010,21 +12123,21 @@
         <v>150</v>
       </c>
       <c r="Y46" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>150</v>
       </c>
       <c r="Z46" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>75</v>
       </c>
-      <c r="AA46" s="16"/>
-      <c r="AB46" s="16"/>
+      <c r="AA46" s="12"/>
+      <c r="AB46" s="12"/>
       <c r="AC46" s="12">
         <f t="shared" si="8"/>
         <v>13.743489583333334</v>
       </c>
       <c r="AD46" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.278645833333334</v>
       </c>
       <c r="AE46" s="12">
@@ -12066,7 +12179,10 @@
         <f t="shared" si="10"/>
         <v>30</v>
       </c>
-      <c r="AR46" s="12"/>
+      <c r="AR46" s="12">
+        <f t="shared" si="11"/>
+        <v>61.44</v>
+      </c>
       <c r="AS46" s="12"/>
       <c r="AT46" s="12"/>
       <c r="AU46" s="12"/>
@@ -12105,7 +12221,7 @@
         <v>481.15</v>
       </c>
       <c r="L47" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-8.5429999999999495</v>
       </c>
       <c r="M47" s="12"/>
@@ -12122,7 +12238,7 @@
         <v>220.98634559999991</v>
       </c>
       <c r="V47" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>94.5214</v>
       </c>
       <c r="W47" s="4">
@@ -12130,7 +12246,7 @@
         <v>207.19060000000002</v>
       </c>
       <c r="X47" s="4">
-        <f t="shared" ref="X47:X48" si="23">W47+V47*$X$1</f>
+        <f t="shared" ref="X47:X48" si="24">W47+V47*$X$1</f>
         <v>383.47301100000004</v>
       </c>
       <c r="Y47" s="4">
@@ -12138,17 +12254,17 @@
         <v>215.89530519300001</v>
       </c>
       <c r="Z47" s="4">
-        <f t="shared" ref="Z47:Z48" si="24">X47*$Z$1</f>
+        <f t="shared" ref="Z47:Z48" si="25">X47*$Z$1</f>
         <v>167.57770580700003</v>
       </c>
-      <c r="AA47" s="16"/>
-      <c r="AB47" s="16"/>
+      <c r="AA47" s="12"/>
+      <c r="AB47" s="12"/>
       <c r="AC47" s="12">
         <f t="shared" si="8"/>
         <v>12.865</v>
       </c>
       <c r="AD47" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.8080032669850432</v>
       </c>
       <c r="AE47" s="12">
@@ -12190,7 +12306,10 @@
         <f t="shared" si="10"/>
         <v>168</v>
       </c>
-      <c r="AR47" s="12"/>
+      <c r="AR47" s="12">
+        <f t="shared" si="11"/>
+        <v>94.5214</v>
+      </c>
       <c r="AS47" s="12"/>
       <c r="AT47" s="12"/>
       <c r="AU47" s="12"/>
@@ -12229,7 +12348,7 @@
         <v>646.79999999999995</v>
       </c>
       <c r="L48" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15.883000000000038</v>
       </c>
       <c r="M48" s="12"/>
@@ -12248,12 +12367,12 @@
         <v>367.2</v>
       </c>
       <c r="V48" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>132.53659999999999</v>
       </c>
       <c r="W48" s="4"/>
       <c r="X48" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>247.18075899999999</v>
       </c>
       <c r="Y48" s="4">
@@ -12261,17 +12380,17 @@
         <v>139.162767317</v>
       </c>
       <c r="Z48" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>108.01799168299999</v>
       </c>
-      <c r="AA48" s="16"/>
-      <c r="AB48" s="16"/>
+      <c r="AA48" s="12"/>
+      <c r="AB48" s="12"/>
       <c r="AC48" s="12">
         <f t="shared" si="8"/>
         <v>12.955718040927565</v>
       </c>
       <c r="AD48" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.090718040927564</v>
       </c>
       <c r="AE48" s="12">
@@ -12313,7 +12432,10 @@
         <f t="shared" si="10"/>
         <v>108</v>
       </c>
-      <c r="AR48" s="12"/>
+      <c r="AR48" s="12">
+        <f t="shared" si="11"/>
+        <v>132.53659999999999</v>
+      </c>
       <c r="AS48" s="12"/>
       <c r="AT48" s="12"/>
       <c r="AU48" s="12"/>
@@ -12344,7 +12466,7 @@
         <v>1.3</v>
       </c>
       <c r="L49" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-1.3</v>
       </c>
       <c r="M49" s="12"/>
@@ -12363,7 +12485,7 @@
         <v>20</v>
       </c>
       <c r="V49" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="W49" s="4">
@@ -12378,14 +12500,14 @@
         <v>10</v>
       </c>
       <c r="Z49" s="4"/>
-      <c r="AA49" s="16"/>
-      <c r="AB49" s="16"/>
+      <c r="AA49" s="12"/>
+      <c r="AB49" s="12"/>
       <c r="AC49" s="12" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD49" s="12" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE49" s="12">
@@ -12429,7 +12551,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR49" s="12"/>
+      <c r="AR49" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AS49" s="12"/>
       <c r="AT49" s="12"/>
       <c r="AU49" s="12"/>
@@ -12468,7 +12593,7 @@
         <v>181</v>
       </c>
       <c r="L50" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-9</v>
       </c>
       <c r="M50" s="12"/>
@@ -12483,7 +12608,7 @@
       <c r="T50" s="12"/>
       <c r="U50" s="12"/>
       <c r="V50" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>34.4</v>
       </c>
       <c r="W50" s="4">
@@ -12499,14 +12624,14 @@
         <v>118.05600000000003</v>
       </c>
       <c r="Z50" s="4"/>
-      <c r="AA50" s="16"/>
-      <c r="AB50" s="16"/>
+      <c r="AA50" s="12"/>
+      <c r="AB50" s="12"/>
       <c r="AC50" s="12">
         <f t="shared" si="8"/>
         <v>12.865</v>
       </c>
       <c r="AD50" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.4331395348837201</v>
       </c>
       <c r="AE50" s="12">
@@ -12548,7 +12673,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR50" s="12"/>
+      <c r="AR50" s="12">
+        <f t="shared" si="11"/>
+        <v>15.48</v>
+      </c>
       <c r="AS50" s="12"/>
       <c r="AT50" s="12"/>
       <c r="AU50" s="12"/>
@@ -12587,7 +12715,7 @@
         <v>454</v>
       </c>
       <c r="L51" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-3</v>
       </c>
       <c r="M51" s="12"/>
@@ -12606,7 +12734,7 @@
         <v>183.6</v>
       </c>
       <c r="V51" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>90.2</v>
       </c>
       <c r="W51" s="4"/>
@@ -12619,14 +12747,14 @@
         <v>0</v>
       </c>
       <c r="Z51" s="4"/>
-      <c r="AA51" s="16"/>
-      <c r="AB51" s="16"/>
+      <c r="AA51" s="12"/>
+      <c r="AB51" s="12"/>
       <c r="AC51" s="12">
         <f t="shared" si="8"/>
         <v>13.766682611973394</v>
       </c>
       <c r="AD51" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13.766682611973394</v>
       </c>
       <c r="AE51" s="12">
@@ -12668,7 +12796,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR51" s="12"/>
+      <c r="AR51" s="12">
+        <f t="shared" si="11"/>
+        <v>40.590000000000003</v>
+      </c>
       <c r="AS51" s="12"/>
       <c r="AT51" s="12"/>
       <c r="AU51" s="12"/>
@@ -12705,7 +12836,7 @@
         <v>48</v>
       </c>
       <c r="L52" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-42</v>
       </c>
       <c r="M52" s="12"/>
@@ -12722,7 +12853,7 @@
         <v>40</v>
       </c>
       <c r="V52" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.2</v>
       </c>
       <c r="W52" s="4">
@@ -12733,18 +12864,18 @@
         <v>50</v>
       </c>
       <c r="Y52" s="4">
-        <f t="shared" ref="Y52:Y53" si="25">X52</f>
+        <f t="shared" ref="Y52:Y53" si="26">X52</f>
         <v>50</v>
       </c>
       <c r="Z52" s="4"/>
-      <c r="AA52" s="16"/>
-      <c r="AB52" s="16"/>
+      <c r="AA52" s="12"/>
+      <c r="AB52" s="12"/>
       <c r="AC52" s="12">
         <f t="shared" si="8"/>
         <v>127.5</v>
       </c>
       <c r="AD52" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>85.833333333333343</v>
       </c>
       <c r="AE52" s="12">
@@ -12786,7 +12917,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR52" s="12"/>
+      <c r="AR52" s="12">
+        <f t="shared" si="11"/>
+        <v>0.48</v>
+      </c>
       <c r="AS52" s="12"/>
       <c r="AT52" s="12"/>
       <c r="AU52" s="12"/>
@@ -12825,7 +12959,7 @@
         <v>86</v>
       </c>
       <c r="L53" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-21</v>
       </c>
       <c r="M53" s="12"/>
@@ -12842,7 +12976,7 @@
       <c r="T53" s="12"/>
       <c r="U53" s="12"/>
       <c r="V53" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13</v>
       </c>
       <c r="W53" s="4">
@@ -12853,18 +12987,18 @@
         <v>20</v>
       </c>
       <c r="Y53" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>20</v>
       </c>
       <c r="Z53" s="4"/>
-      <c r="AA53" s="16"/>
-      <c r="AB53" s="16"/>
+      <c r="AA53" s="12"/>
+      <c r="AB53" s="12"/>
       <c r="AC53" s="12">
         <f t="shared" si="8"/>
         <v>15.846153846153847</v>
       </c>
       <c r="AD53" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14.307692307692308</v>
       </c>
       <c r="AE53" s="12">
@@ -12906,7 +13040,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR53" s="12"/>
+      <c r="AR53" s="12">
+        <f t="shared" si="11"/>
+        <v>5.2</v>
+      </c>
       <c r="AS53" s="12"/>
       <c r="AT53" s="12"/>
       <c r="AU53" s="12"/>
@@ -12945,7 +13082,7 @@
         <v>614.5</v>
       </c>
       <c r="L54" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.0399999999999636</v>
       </c>
       <c r="M54" s="12"/>
@@ -12964,7 +13101,7 @@
         <v>367.2</v>
       </c>
       <c r="V54" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>123.30799999999999</v>
       </c>
       <c r="W54" s="4"/>
@@ -12977,14 +13114,14 @@
         <v>0</v>
       </c>
       <c r="Z54" s="4"/>
-      <c r="AA54" s="16"/>
-      <c r="AB54" s="16"/>
+      <c r="AA54" s="12"/>
+      <c r="AB54" s="12"/>
       <c r="AC54" s="12">
         <f t="shared" si="8"/>
         <v>14.53567267654978</v>
       </c>
       <c r="AD54" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14.53567267654978</v>
       </c>
       <c r="AE54" s="12">
@@ -13026,7 +13163,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR54" s="12"/>
+      <c r="AR54" s="12">
+        <f t="shared" si="11"/>
+        <v>123.30799999999999</v>
+      </c>
       <c r="AS54" s="12"/>
       <c r="AT54" s="12"/>
       <c r="AU54" s="12"/>
@@ -13045,11 +13185,11 @@
       <c r="D55" s="12">
         <v>100</v>
       </c>
-      <c r="E55" s="15">
+      <c r="E55" s="14">
         <f>279+E128</f>
         <v>422</v>
       </c>
-      <c r="F55" s="15">
+      <c r="F55" s="14">
         <f>113+F128</f>
         <v>165</v>
       </c>
@@ -13067,7 +13207,7 @@
         <v>278</v>
       </c>
       <c r="L55" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>144</v>
       </c>
       <c r="M55" s="12"/>
@@ -13084,7 +13224,7 @@
         <v>244.8</v>
       </c>
       <c r="V55" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>84.4</v>
       </c>
       <c r="W55" s="4">
@@ -13092,7 +13232,7 @@
         <v>363.40000000000009</v>
       </c>
       <c r="X55" s="4">
-        <f t="shared" ref="X55:X56" si="26">W55+V55*$X$1</f>
+        <f t="shared" ref="X55:X56" si="27">W55+V55*$X$1</f>
         <v>520.80600000000004</v>
       </c>
       <c r="Y55" s="4">
@@ -13100,17 +13240,17 @@
         <v>293.21377800000005</v>
       </c>
       <c r="Z55" s="4">
-        <f t="shared" ref="Z55:Z56" si="27">X55*$Z$1</f>
+        <f t="shared" ref="Z55:Z56" si="28">X55*$Z$1</f>
         <v>227.59222200000002</v>
       </c>
-      <c r="AA55" s="16"/>
-      <c r="AB55" s="16"/>
+      <c r="AA55" s="12"/>
+      <c r="AB55" s="12"/>
       <c r="AC55" s="12">
         <f t="shared" si="8"/>
         <v>12.865</v>
       </c>
       <c r="AD55" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.6943127962085303</v>
       </c>
       <c r="AE55" s="12">
@@ -13152,7 +13292,10 @@
         <f t="shared" si="10"/>
         <v>23</v>
       </c>
-      <c r="AR55" s="12"/>
+      <c r="AR55" s="12">
+        <f t="shared" si="11"/>
+        <v>8.4400000000000013</v>
+      </c>
       <c r="AS55" s="12"/>
       <c r="AT55" s="12"/>
       <c r="AU55" s="12"/>
@@ -13191,7 +13334,7 @@
         <v>889.65</v>
       </c>
       <c r="L56" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>14.161000000000058</v>
       </c>
       <c r="M56" s="12"/>
@@ -13210,7 +13353,7 @@
         <v>428.4</v>
       </c>
       <c r="V56" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>180.76220000000001</v>
       </c>
       <c r="W56" s="4">
@@ -13218,7 +13361,7 @@
         <v>33.966541599999914</v>
       </c>
       <c r="X56" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>371.08804459999993</v>
       </c>
       <c r="Y56" s="4">
@@ -13226,17 +13369,17 @@
         <v>208.92256910979995</v>
       </c>
       <c r="Z56" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>162.16547549019998</v>
       </c>
-      <c r="AA56" s="16"/>
-      <c r="AB56" s="16"/>
+      <c r="AA56" s="12"/>
+      <c r="AB56" s="12"/>
       <c r="AC56" s="12">
         <f t="shared" si="8"/>
         <v>12.865</v>
       </c>
       <c r="AD56" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.812092674242734</v>
       </c>
       <c r="AE56" s="12">
@@ -13278,7 +13421,10 @@
         <f t="shared" si="10"/>
         <v>162</v>
       </c>
-      <c r="AR56" s="12"/>
+      <c r="AR56" s="12">
+        <f t="shared" si="11"/>
+        <v>180.76220000000001</v>
+      </c>
       <c r="AS56" s="12"/>
       <c r="AT56" s="12"/>
       <c r="AU56" s="12"/>
@@ -13315,7 +13461,7 @@
         <v>90.09</v>
       </c>
       <c r="L57" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.2800000000000011</v>
       </c>
       <c r="M57" s="12"/>
@@ -13330,7 +13476,7 @@
       <c r="T57" s="12"/>
       <c r="U57" s="12"/>
       <c r="V57" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>18.474</v>
       </c>
       <c r="W57" s="4">
@@ -13346,14 +13492,14 @@
         <v>12.800000000000011</v>
       </c>
       <c r="Z57" s="4"/>
-      <c r="AA57" s="16"/>
-      <c r="AB57" s="16"/>
+      <c r="AA57" s="12"/>
+      <c r="AB57" s="12"/>
       <c r="AC57" s="12">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="AD57" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.307134350979755</v>
       </c>
       <c r="AE57" s="12">
@@ -13395,7 +13541,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR57" s="12"/>
+      <c r="AR57" s="12">
+        <f t="shared" si="11"/>
+        <v>18.474</v>
+      </c>
       <c r="AS57" s="12"/>
       <c r="AT57" s="12"/>
       <c r="AU57" s="12"/>
@@ -13432,7 +13581,7 @@
         <v>246</v>
       </c>
       <c r="L58" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M58" s="12"/>
@@ -13447,7 +13596,7 @@
       <c r="T58" s="12"/>
       <c r="U58" s="12"/>
       <c r="V58" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>49.2</v>
       </c>
       <c r="W58" s="4">
@@ -13466,14 +13615,14 @@
         <f>X58*$Z$1</f>
         <v>146.33294600000002</v>
       </c>
-      <c r="AA58" s="16"/>
-      <c r="AB58" s="16"/>
+      <c r="AA58" s="12"/>
+      <c r="AB58" s="12"/>
       <c r="AC58" s="12">
         <f t="shared" si="8"/>
         <v>12.865</v>
       </c>
       <c r="AD58" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.058943089430894</v>
       </c>
       <c r="AE58" s="12">
@@ -13515,7 +13664,10 @@
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
-      <c r="AR58" s="12"/>
+      <c r="AR58" s="12">
+        <f t="shared" si="11"/>
+        <v>4.9200000000000008</v>
+      </c>
       <c r="AS58" s="12"/>
       <c r="AT58" s="12"/>
       <c r="AU58" s="12"/>
@@ -13554,7 +13706,7 @@
         <v>208</v>
       </c>
       <c r="L59" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-4</v>
       </c>
       <c r="M59" s="12"/>
@@ -13569,7 +13721,7 @@
       <c r="T59" s="12"/>
       <c r="U59" s="12"/>
       <c r="V59" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>40.799999999999997</v>
       </c>
       <c r="W59" s="4"/>
@@ -13582,14 +13734,14 @@
         <v>0</v>
       </c>
       <c r="Z59" s="4"/>
-      <c r="AA59" s="16"/>
-      <c r="AB59" s="16"/>
+      <c r="AA59" s="12"/>
+      <c r="AB59" s="12"/>
       <c r="AC59" s="12">
         <f t="shared" si="8"/>
         <v>12.529411764705882</v>
       </c>
       <c r="AD59" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.529411764705882</v>
       </c>
       <c r="AE59" s="12">
@@ -13631,7 +13783,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR59" s="12"/>
+      <c r="AR59" s="12">
+        <f t="shared" si="11"/>
+        <v>16.32</v>
+      </c>
       <c r="AS59" s="12"/>
       <c r="AT59" s="12"/>
       <c r="AU59" s="12"/>
@@ -13670,7 +13825,7 @@
         <v>407.3</v>
       </c>
       <c r="L60" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-42.785000000000025</v>
       </c>
       <c r="M60" s="12"/>
@@ -13689,7 +13844,7 @@
         <v>200</v>
       </c>
       <c r="V60" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>72.902999999999992</v>
       </c>
       <c r="W60" s="4"/>
@@ -13698,18 +13853,18 @@
         <v>0</v>
       </c>
       <c r="Y60" s="4">
-        <f t="shared" ref="Y60:Y62" si="28">X60</f>
+        <f t="shared" ref="Y60:Y62" si="29">X60</f>
         <v>0</v>
       </c>
       <c r="Z60" s="4"/>
-      <c r="AA60" s="16"/>
-      <c r="AB60" s="16"/>
+      <c r="AA60" s="12"/>
+      <c r="AB60" s="12"/>
       <c r="AC60" s="12">
         <f t="shared" si="8"/>
         <v>17.321152764632462</v>
       </c>
       <c r="AD60" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>17.321152764632462</v>
       </c>
       <c r="AE60" s="12">
@@ -13751,7 +13906,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR60" s="12"/>
+      <c r="AR60" s="12">
+        <f t="shared" si="11"/>
+        <v>72.902999999999992</v>
+      </c>
       <c r="AS60" s="12"/>
       <c r="AT60" s="12"/>
       <c r="AU60" s="12"/>
@@ -13790,7 +13948,7 @@
         <v>516.04999999999995</v>
       </c>
       <c r="L61" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-72.868999999999971</v>
       </c>
       <c r="M61" s="12"/>
@@ -13811,7 +13969,7 @@
         <v>100</v>
       </c>
       <c r="V61" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>88.636200000000002</v>
       </c>
       <c r="W61" s="4">
@@ -13823,21 +13981,21 @@
         <v>270.29184899999984</v>
       </c>
       <c r="Y61" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>270.29184899999984</v>
       </c>
       <c r="Z61" s="4">
         <f>0.5*X61</f>
         <v>135.14592449999992</v>
       </c>
-      <c r="AA61" s="16"/>
-      <c r="AB61" s="16"/>
+      <c r="AA61" s="12"/>
+      <c r="AB61" s="12"/>
       <c r="AC61" s="12">
         <f t="shared" si="8"/>
         <v>12.524726065648119</v>
       </c>
       <c r="AD61" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.9505478687037581</v>
       </c>
       <c r="AE61" s="12">
@@ -13881,7 +14039,10 @@
         <f t="shared" si="10"/>
         <v>135</v>
       </c>
-      <c r="AR61" s="12"/>
+      <c r="AR61" s="12">
+        <f t="shared" si="11"/>
+        <v>88.636200000000002</v>
+      </c>
       <c r="AS61" s="12"/>
       <c r="AT61" s="12"/>
       <c r="AU61" s="12"/>
@@ -13920,7 +14081,7 @@
         <v>1189</v>
       </c>
       <c r="L62" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-24</v>
       </c>
       <c r="M62" s="12"/>
@@ -13939,7 +14100,7 @@
         <v>500</v>
       </c>
       <c r="V62" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>233</v>
       </c>
       <c r="W62" s="4"/>
@@ -13948,18 +14109,18 @@
         <v>0</v>
       </c>
       <c r="Y62" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Z62" s="4"/>
-      <c r="AA62" s="16"/>
-      <c r="AB62" s="16"/>
+      <c r="AA62" s="12"/>
+      <c r="AB62" s="12"/>
       <c r="AC62" s="12">
         <f t="shared" si="8"/>
         <v>12.135716738197425</v>
       </c>
       <c r="AD62" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.135716738197425</v>
       </c>
       <c r="AE62" s="12">
@@ -14001,7 +14162,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR62" s="12"/>
+      <c r="AR62" s="12">
+        <f t="shared" si="11"/>
+        <v>93.2</v>
+      </c>
       <c r="AS62" s="12"/>
       <c r="AT62" s="12"/>
       <c r="AU62" s="12"/>
@@ -14040,7 +14204,7 @@
         <v>754</v>
       </c>
       <c r="L63" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-12</v>
       </c>
       <c r="M63" s="12"/>
@@ -14057,7 +14221,7 @@
         <v>275.39999999999998</v>
       </c>
       <c r="V63" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>148.4</v>
       </c>
       <c r="W63" s="4">
@@ -14076,14 +14240,14 @@
         <f>X63*$Z$1</f>
         <v>496.15494200000012</v>
       </c>
-      <c r="AA63" s="16"/>
-      <c r="AB63" s="16"/>
+      <c r="AA63" s="12"/>
+      <c r="AB63" s="12"/>
       <c r="AC63" s="12">
         <f t="shared" si="8"/>
         <v>10.865</v>
       </c>
       <c r="AD63" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.214285714285714</v>
       </c>
       <c r="AE63" s="12">
@@ -14125,7 +14289,10 @@
         <f t="shared" si="10"/>
         <v>198</v>
       </c>
-      <c r="AR63" s="12"/>
+      <c r="AR63" s="12">
+        <f t="shared" si="11"/>
+        <v>59.360000000000007</v>
+      </c>
       <c r="AS63" s="12"/>
       <c r="AT63" s="12"/>
       <c r="AU63" s="12"/>
@@ -14162,7 +14329,7 @@
         <v>427.42500000000001</v>
       </c>
       <c r="L64" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-73.53000000000003</v>
       </c>
       <c r="M64" s="12"/>
@@ -14181,7 +14348,7 @@
         <v>20</v>
       </c>
       <c r="V64" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>70.778999999999996</v>
       </c>
       <c r="W64" s="4">
@@ -14192,21 +14359,21 @@
         <v>200</v>
       </c>
       <c r="Y64" s="4">
-        <f t="shared" ref="Y64:Y67" si="29">X64</f>
+        <f t="shared" ref="Y64:Y67" si="30">X64</f>
         <v>200</v>
       </c>
       <c r="Z64" s="4">
         <f>0.5*X64</f>
         <v>100</v>
       </c>
-      <c r="AA64" s="16"/>
-      <c r="AB64" s="16"/>
+      <c r="AA64" s="12"/>
+      <c r="AB64" s="12"/>
       <c r="AC64" s="12">
         <f t="shared" si="8"/>
         <v>5.0478249198208509</v>
       </c>
       <c r="AD64" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.80927958857853322</v>
       </c>
       <c r="AE64" s="12">
@@ -14248,7 +14415,10 @@
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR64" s="12"/>
+      <c r="AR64" s="12">
+        <f t="shared" si="11"/>
+        <v>70.778999999999996</v>
+      </c>
       <c r="AS64" s="12"/>
       <c r="AT64" s="12"/>
       <c r="AU64" s="12"/>
@@ -14283,7 +14453,7 @@
         <v>41.8</v>
       </c>
       <c r="L65" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-33.964999999999996</v>
       </c>
       <c r="M65" s="12"/>
@@ -14302,7 +14472,7 @@
         <v>100</v>
       </c>
       <c r="V65" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.5669999999999999</v>
       </c>
       <c r="W65" s="4">
@@ -14313,18 +14483,18 @@
         <v>100</v>
       </c>
       <c r="Y65" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>100</v>
       </c>
       <c r="Z65" s="4"/>
-      <c r="AA65" s="16"/>
-      <c r="AB65" s="16"/>
+      <c r="AA65" s="12"/>
+      <c r="AB65" s="12"/>
       <c r="AC65" s="12">
         <f t="shared" si="8"/>
         <v>126.86662412252713</v>
       </c>
       <c r="AD65" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>63.050414805360568</v>
       </c>
       <c r="AE65" s="12">
@@ -14366,7 +14536,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR65" s="12"/>
+      <c r="AR65" s="12">
+        <f t="shared" si="11"/>
+        <v>1.5669999999999999</v>
+      </c>
       <c r="AS65" s="12"/>
       <c r="AT65" s="12"/>
       <c r="AU65" s="12"/>
@@ -14403,7 +14576,7 @@
         <v>302.5</v>
       </c>
       <c r="L66" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-130.83000000000001</v>
       </c>
       <c r="M66" s="12"/>
@@ -14420,7 +14593,7 @@
         <v>200</v>
       </c>
       <c r="V66" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>34.333999999999996</v>
       </c>
       <c r="W66" s="4">
@@ -14431,15 +14604,15 @@
         <v>200</v>
       </c>
       <c r="Y66" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>200</v>
       </c>
       <c r="Z66" s="4"/>
-      <c r="AA66" s="16">
+      <c r="AA66" s="12">
         <f>VLOOKUP(A66,[1]Sheet!$A:$Y,24,0)</f>
         <v>200</v>
       </c>
-      <c r="AB66" s="16" t="str">
+      <c r="AB66" s="12" t="str">
         <f>VLOOKUP(A66,[1]Sheet!$A:$Y,25,0)</f>
         <v>промо жц</v>
       </c>
@@ -14448,7 +14621,7 @@
         <v>20.384400302906741</v>
       </c>
       <c r="AD66" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14.559270693772937</v>
       </c>
       <c r="AE66" s="12">
@@ -14490,7 +14663,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR66" s="12"/>
+      <c r="AR66" s="12">
+        <f t="shared" si="11"/>
+        <v>34.333999999999996</v>
+      </c>
       <c r="AS66" s="12"/>
       <c r="AT66" s="12"/>
       <c r="AU66" s="12"/>
@@ -14529,7 +14705,7 @@
         <v>252.05</v>
       </c>
       <c r="L67" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-84.485000000000014</v>
       </c>
       <c r="M67" s="12"/>
@@ -14552,7 +14728,7 @@
         <v>100</v>
       </c>
       <c r="V67" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>33.512999999999998</v>
       </c>
       <c r="W67" s="4">
@@ -14563,21 +14739,21 @@
         <v>150</v>
       </c>
       <c r="Y67" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>150</v>
       </c>
       <c r="Z67" s="4">
         <f>0.5*X67</f>
         <v>75</v>
       </c>
-      <c r="AA67" s="16"/>
-      <c r="AB67" s="16"/>
+      <c r="AA67" s="12"/>
+      <c r="AB67" s="12"/>
       <c r="AC67" s="12">
         <f t="shared" si="8"/>
         <v>9.342314922567363</v>
       </c>
       <c r="AD67" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.6285023722137679</v>
       </c>
       <c r="AE67" s="12">
@@ -14619,7 +14795,10 @@
         <f t="shared" si="10"/>
         <v>75</v>
       </c>
-      <c r="AR67" s="12"/>
+      <c r="AR67" s="12">
+        <f t="shared" si="11"/>
+        <v>33.512999999999998</v>
+      </c>
       <c r="AS67" s="12"/>
       <c r="AT67" s="12"/>
       <c r="AU67" s="12"/>
@@ -14656,7 +14835,7 @@
         <v>17</v>
       </c>
       <c r="L68" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-11</v>
       </c>
       <c r="M68" s="12"/>
@@ -14671,7 +14850,7 @@
       <c r="T68" s="12"/>
       <c r="U68" s="12"/>
       <c r="V68" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.2</v>
       </c>
       <c r="W68" s="4"/>
@@ -14684,14 +14863,14 @@
         <v>0</v>
       </c>
       <c r="Z68" s="4"/>
-      <c r="AA68" s="16"/>
-      <c r="AB68" s="16"/>
+      <c r="AA68" s="12"/>
+      <c r="AB68" s="12"/>
       <c r="AC68" s="12">
         <f t="shared" si="8"/>
         <v>19.166666666666668</v>
       </c>
       <c r="AD68" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>19.166666666666668</v>
       </c>
       <c r="AE68" s="12">
@@ -14735,7 +14914,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR68" s="12"/>
+      <c r="AR68" s="12">
+        <f t="shared" si="11"/>
+        <v>0.72</v>
+      </c>
       <c r="AS68" s="12"/>
       <c r="AT68" s="12"/>
       <c r="AU68" s="12"/>
@@ -14774,7 +14956,7 @@
         <v>258.315</v>
       </c>
       <c r="L69" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-50.657000000000011</v>
       </c>
       <c r="M69" s="12"/>
@@ -14793,7 +14975,7 @@
         <v>100</v>
       </c>
       <c r="V69" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>41.531599999999997</v>
       </c>
       <c r="W69" s="4">
@@ -14809,14 +14991,14 @@
         <v>93.56239999999994</v>
       </c>
       <c r="Z69" s="4"/>
-      <c r="AA69" s="16"/>
-      <c r="AB69" s="16"/>
+      <c r="AA69" s="12"/>
+      <c r="AB69" s="12"/>
       <c r="AC69" s="12">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="AD69" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.7471997226208469</v>
       </c>
       <c r="AE69" s="12">
@@ -14860,7 +15042,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR69" s="12"/>
+      <c r="AR69" s="12">
+        <f t="shared" si="11"/>
+        <v>41.531599999999997</v>
+      </c>
       <c r="AS69" s="12"/>
       <c r="AT69" s="12"/>
       <c r="AU69" s="12"/>
@@ -14899,7 +15084,7 @@
         <v>118</v>
       </c>
       <c r="L70" s="12">
-        <f t="shared" ref="L70:L101" si="30">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="31">E70-K70</f>
         <v>0</v>
       </c>
       <c r="M70" s="12"/>
@@ -14914,7 +15099,7 @@
       <c r="T70" s="12"/>
       <c r="U70" s="12"/>
       <c r="V70" s="12">
-        <f t="shared" ref="V70:V101" si="31">E70/5</f>
+        <f t="shared" ref="V70:V101" si="32">E70/5</f>
         <v>23.6</v>
       </c>
       <c r="W70" s="4">
@@ -14930,14 +15115,14 @@
         <v>29.100000000000023</v>
       </c>
       <c r="Z70" s="4"/>
-      <c r="AA70" s="16"/>
-      <c r="AB70" s="16"/>
+      <c r="AA70" s="12"/>
+      <c r="AB70" s="12"/>
       <c r="AC70" s="12">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="AD70" s="12">
-        <f t="shared" ref="AD70:AD101" si="32">(F70+O70+P70+Q70+R70+S70+T70+U70)/V70</f>
+        <f t="shared" ref="AD70:AD101" si="33">(F70+O70+P70+Q70+R70+S70+T70+U70)/V70</f>
         <v>9.7669491525423719</v>
       </c>
       <c r="AE70" s="12">
@@ -14979,7 +15164,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AR70" s="12"/>
+      <c r="AR70" s="12">
+        <f t="shared" si="11"/>
+        <v>14.16</v>
+      </c>
       <c r="AS70" s="12"/>
       <c r="AT70" s="12"/>
       <c r="AU70" s="12"/>
@@ -15018,7 +15206,7 @@
         <v>55</v>
       </c>
       <c r="L71" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-11</v>
       </c>
       <c r="M71" s="12"/>
@@ -15033,7 +15221,7 @@
       <c r="T71" s="12"/>
       <c r="U71" s="12"/>
       <c r="V71" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="W71" s="4">
@@ -15041,22 +15229,22 @@
         <v>28.800000000000011</v>
       </c>
       <c r="X71" s="4">
-        <f t="shared" ref="X71:X129" si="33">W71</f>
+        <f t="shared" ref="X71:X129" si="34">W71</f>
         <v>28.800000000000011</v>
       </c>
       <c r="Y71" s="4">
-        <f t="shared" ref="Y71:Y129" si="34">X71-Z71</f>
+        <f t="shared" ref="Y71:Y129" si="35">X71-Z71</f>
         <v>28.800000000000011</v>
       </c>
       <c r="Z71" s="4"/>
-      <c r="AA71" s="16"/>
-      <c r="AB71" s="16"/>
+      <c r="AA71" s="12"/>
+      <c r="AB71" s="12"/>
       <c r="AC71" s="12">
-        <f t="shared" ref="AC71:AC129" si="35">(F71+O71+P71+Q71+R71+S71+T71+U71+Y71+Z71)/V71</f>
+        <f t="shared" ref="AC71:AC129" si="36">(F71+O71+P71+Q71+R71+S71+T71+U71+Y71+Z71)/V71</f>
         <v>11</v>
       </c>
       <c r="AD71" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.7272727272727266</v>
       </c>
       <c r="AE71" s="12">
@@ -15091,14 +15279,17 @@
       </c>
       <c r="AO71" s="12"/>
       <c r="AP71" s="12">
-        <f t="shared" ref="AP71:AQ129" si="36">ROUND(G71*Y71,0)</f>
+        <f t="shared" ref="AP71:AP129" si="37">ROUND(G71*Y71,0)</f>
         <v>17</v>
       </c>
       <c r="AQ71" s="12">
-        <f t="shared" ref="AQ71:AQ129" si="37">ROUND(G71*Z71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR71" s="12"/>
+        <f t="shared" ref="AQ71:AQ129" si="38">ROUND(G71*Z71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR71" s="12">
+        <f t="shared" ref="AR71:AR129" si="39">V71*G71</f>
+        <v>5.28</v>
+      </c>
       <c r="AS71" s="12"/>
       <c r="AT71" s="12"/>
       <c r="AU71" s="12"/>
@@ -15137,7 +15328,7 @@
         <v>151</v>
       </c>
       <c r="L72" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1</v>
       </c>
       <c r="M72" s="12"/>
@@ -15154,29 +15345,29 @@
       <c r="T72" s="12"/>
       <c r="U72" s="12"/>
       <c r="V72" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>30</v>
       </c>
       <c r="W72" s="4">
         <v>50</v>
       </c>
       <c r="X72" s="4">
+        <f t="shared" si="34"/>
+        <v>50</v>
+      </c>
+      <c r="Y72" s="4">
+        <f t="shared" ref="Y72:Y74" si="40">X72</f>
+        <v>50</v>
+      </c>
+      <c r="Z72" s="4"/>
+      <c r="AA72" s="12"/>
+      <c r="AB72" s="12"/>
+      <c r="AC72" s="12">
+        <f t="shared" si="36"/>
+        <v>11.753333333333332</v>
+      </c>
+      <c r="AD72" s="12">
         <f t="shared" si="33"/>
-        <v>50</v>
-      </c>
-      <c r="Y72" s="4">
-        <f t="shared" ref="Y72:Y74" si="38">X72</f>
-        <v>50</v>
-      </c>
-      <c r="Z72" s="4"/>
-      <c r="AA72" s="16"/>
-      <c r="AB72" s="16"/>
-      <c r="AC72" s="12">
-        <f t="shared" si="35"/>
-        <v>11.753333333333332</v>
-      </c>
-      <c r="AD72" s="12">
-        <f t="shared" si="32"/>
         <v>10.086666666666666</v>
       </c>
       <c r="AE72" s="12">
@@ -15211,14 +15402,17 @@
       </c>
       <c r="AO72" s="12"/>
       <c r="AP72" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="AQ72" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR72" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR72" s="12">
+        <f t="shared" si="39"/>
+        <v>12</v>
+      </c>
       <c r="AS72" s="12"/>
       <c r="AT72" s="12"/>
       <c r="AU72" s="12"/>
@@ -15257,7 +15451,7 @@
         <v>189</v>
       </c>
       <c r="L73" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1</v>
       </c>
       <c r="M73" s="12"/>
@@ -15274,7 +15468,7 @@
       <c r="T73" s="12"/>
       <c r="U73" s="12"/>
       <c r="V73" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>37.6</v>
       </c>
       <c r="W73" s="4">
@@ -15282,25 +15476,25 @@
         <v>129.60000000000002</v>
       </c>
       <c r="X73" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>129.60000000000002</v>
       </c>
       <c r="Y73" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>129.60000000000002</v>
       </c>
       <c r="Z73" s="4">
         <f>0.5*X73</f>
         <v>64.800000000000011</v>
       </c>
-      <c r="AA73" s="16"/>
-      <c r="AB73" s="16"/>
+      <c r="AA73" s="12"/>
+      <c r="AB73" s="12"/>
       <c r="AC73" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.723404255319149</v>
       </c>
       <c r="AD73" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.5531914893617023</v>
       </c>
       <c r="AE73" s="12">
@@ -15335,14 +15529,17 @@
       </c>
       <c r="AO73" s="12"/>
       <c r="AP73" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>43</v>
       </c>
       <c r="AQ73" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>21</v>
       </c>
-      <c r="AR73" s="12"/>
+      <c r="AR73" s="12">
+        <f t="shared" si="39"/>
+        <v>12.408000000000001</v>
+      </c>
       <c r="AS73" s="12"/>
       <c r="AT73" s="12"/>
       <c r="AU73" s="12"/>
@@ -15381,7 +15578,7 @@
         <v>160</v>
       </c>
       <c r="L74" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-5</v>
       </c>
       <c r="M74" s="12"/>
@@ -15398,29 +15595,29 @@
       <c r="T74" s="12"/>
       <c r="U74" s="12"/>
       <c r="V74" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="W74" s="4">
         <v>100</v>
       </c>
       <c r="X74" s="4">
+        <f t="shared" si="34"/>
+        <v>100</v>
+      </c>
+      <c r="Y74" s="4">
+        <f t="shared" si="40"/>
+        <v>100</v>
+      </c>
+      <c r="Z74" s="4"/>
+      <c r="AA74" s="12"/>
+      <c r="AB74" s="12"/>
+      <c r="AC74" s="12">
+        <f t="shared" si="36"/>
+        <v>4.5032258064516126</v>
+      </c>
+      <c r="AD74" s="12">
         <f t="shared" si="33"/>
-        <v>100</v>
-      </c>
-      <c r="Y74" s="4">
-        <f t="shared" si="38"/>
-        <v>100</v>
-      </c>
-      <c r="Z74" s="4"/>
-      <c r="AA74" s="16"/>
-      <c r="AB74" s="16"/>
-      <c r="AC74" s="12">
-        <f t="shared" si="35"/>
-        <v>4.5032258064516126</v>
-      </c>
-      <c r="AD74" s="12">
-        <f t="shared" si="32"/>
         <v>1.2774193548387094</v>
       </c>
       <c r="AE74" s="12">
@@ -15455,14 +15652,17 @@
       </c>
       <c r="AO74" s="12"/>
       <c r="AP74" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>35</v>
       </c>
       <c r="AQ74" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR74" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR74" s="12">
+        <f t="shared" si="39"/>
+        <v>10.85</v>
+      </c>
       <c r="AS74" s="12"/>
       <c r="AT74" s="12"/>
       <c r="AU74" s="12"/>
@@ -15501,7 +15701,7 @@
         <v>580</v>
       </c>
       <c r="L75" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-8</v>
       </c>
       <c r="M75" s="12"/>
@@ -15518,7 +15718,7 @@
         <v>275.39999999999998</v>
       </c>
       <c r="V75" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>114.4</v>
       </c>
       <c r="W75" s="4">
@@ -15526,25 +15726,25 @@
         <v>304.40000000000009</v>
       </c>
       <c r="X75" s="4">
-        <f t="shared" ref="X75:X76" si="39">W75+V75*$X$1</f>
+        <f t="shared" ref="X75:X76" si="41">W75+V75*$X$1</f>
         <v>517.75600000000009</v>
       </c>
       <c r="Y75" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>291.49662800000004</v>
       </c>
       <c r="Z75" s="4">
-        <f t="shared" ref="Z75:Z76" si="40">X75*$Z$1</f>
+        <f t="shared" ref="Z75:Z76" si="42">X75*$Z$1</f>
         <v>226.25937200000004</v>
       </c>
-      <c r="AA75" s="16"/>
-      <c r="AB75" s="16"/>
+      <c r="AA75" s="12"/>
+      <c r="AB75" s="12"/>
       <c r="AC75" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.865</v>
       </c>
       <c r="AD75" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.3391608391608383</v>
       </c>
       <c r="AE75" s="12">
@@ -15579,14 +15779,17 @@
       </c>
       <c r="AO75" s="12"/>
       <c r="AP75" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>108</v>
       </c>
       <c r="AQ75" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>84</v>
       </c>
-      <c r="AR75" s="12"/>
+      <c r="AR75" s="12">
+        <f t="shared" si="39"/>
+        <v>42.328000000000003</v>
+      </c>
       <c r="AS75" s="12"/>
       <c r="AT75" s="12"/>
       <c r="AU75" s="12"/>
@@ -15625,7 +15828,7 @@
         <v>243</v>
       </c>
       <c r="L76" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M76" s="12"/>
@@ -15640,7 +15843,7 @@
       <c r="T76" s="12"/>
       <c r="U76" s="12"/>
       <c r="V76" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>48.6</v>
       </c>
       <c r="W76" s="4">
@@ -15648,25 +15851,25 @@
         <v>280.5</v>
       </c>
       <c r="X76" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>371.13900000000001</v>
       </c>
       <c r="Y76" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>208.951257</v>
       </c>
       <c r="Z76" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>162.18774300000001</v>
       </c>
-      <c r="AA76" s="16"/>
-      <c r="AB76" s="16"/>
+      <c r="AA76" s="12"/>
+      <c r="AB76" s="12"/>
       <c r="AC76" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.865</v>
       </c>
       <c r="AD76" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.2283950617283947</v>
       </c>
       <c r="AE76" s="12">
@@ -15701,14 +15904,17 @@
       </c>
       <c r="AO76" s="12"/>
       <c r="AP76" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>125</v>
       </c>
       <c r="AQ76" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>97</v>
       </c>
-      <c r="AR76" s="12"/>
+      <c r="AR76" s="12">
+        <f t="shared" si="39"/>
+        <v>29.16</v>
+      </c>
       <c r="AS76" s="12"/>
       <c r="AT76" s="12"/>
       <c r="AU76" s="12"/>
@@ -15747,7 +15953,7 @@
         <v>76</v>
       </c>
       <c r="L77" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-31</v>
       </c>
       <c r="M77" s="12"/>
@@ -15762,7 +15968,7 @@
       <c r="T77" s="12"/>
       <c r="U77" s="12"/>
       <c r="V77" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9</v>
       </c>
       <c r="W77" s="4">
@@ -15770,22 +15976,22 @@
         <v>19</v>
       </c>
       <c r="X77" s="4">
-        <f t="shared" si="33"/>
-        <v>19</v>
-      </c>
-      <c r="Y77" s="4">
         <f t="shared" si="34"/>
         <v>19</v>
       </c>
+      <c r="Y77" s="4">
+        <f t="shared" si="35"/>
+        <v>19</v>
+      </c>
       <c r="Z77" s="4"/>
-      <c r="AA77" s="16"/>
-      <c r="AB77" s="16"/>
+      <c r="AA77" s="12"/>
+      <c r="AB77" s="12"/>
       <c r="AC77" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11</v>
       </c>
       <c r="AD77" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.8888888888888893</v>
       </c>
       <c r="AE77" s="12">
@@ -15820,14 +16026,17 @@
       </c>
       <c r="AO77" s="12"/>
       <c r="AP77" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>6</v>
       </c>
       <c r="AQ77" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR77" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR77" s="12">
+        <f t="shared" si="39"/>
+        <v>2.97</v>
+      </c>
       <c r="AS77" s="12"/>
       <c r="AT77" s="12"/>
       <c r="AU77" s="12"/>
@@ -15866,7 +16075,7 @@
         <v>285</v>
       </c>
       <c r="L78" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-3</v>
       </c>
       <c r="M78" s="12"/>
@@ -15881,7 +16090,7 @@
       <c r="T78" s="12"/>
       <c r="U78" s="12"/>
       <c r="V78" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>56.4</v>
       </c>
       <c r="W78" s="4">
@@ -15893,21 +16102,21 @@
         <v>267.23599999999993</v>
       </c>
       <c r="Y78" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>150.45386799999994</v>
       </c>
       <c r="Z78" s="4">
         <f>X78*$Z$1</f>
         <v>116.78213199999998</v>
       </c>
-      <c r="AA78" s="16"/>
-      <c r="AB78" s="16"/>
+      <c r="AA78" s="12"/>
+      <c r="AB78" s="12"/>
       <c r="AC78" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.864999999999998</v>
       </c>
       <c r="AD78" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.12677304964539</v>
       </c>
       <c r="AE78" s="12">
@@ -15942,14 +16151,17 @@
       </c>
       <c r="AO78" s="12"/>
       <c r="AP78" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>60</v>
       </c>
       <c r="AQ78" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>47</v>
       </c>
-      <c r="AR78" s="12"/>
+      <c r="AR78" s="12">
+        <f t="shared" si="39"/>
+        <v>22.560000000000002</v>
+      </c>
       <c r="AS78" s="12"/>
       <c r="AT78" s="12"/>
       <c r="AU78" s="12"/>
@@ -15984,7 +16196,7 @@
         <v>228</v>
       </c>
       <c r="L79" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-177</v>
       </c>
       <c r="M79" s="12"/>
@@ -16003,29 +16215,29 @@
         <v>50</v>
       </c>
       <c r="V79" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>10.199999999999999</v>
       </c>
       <c r="W79" s="4">
         <v>100</v>
       </c>
       <c r="X79" s="4">
+        <f t="shared" si="34"/>
+        <v>100</v>
+      </c>
+      <c r="Y79" s="4">
+        <f t="shared" ref="Y79:Y80" si="43">X79</f>
+        <v>100</v>
+      </c>
+      <c r="Z79" s="4"/>
+      <c r="AA79" s="12"/>
+      <c r="AB79" s="12"/>
+      <c r="AC79" s="12">
+        <f t="shared" si="36"/>
+        <v>14.313725490196079</v>
+      </c>
+      <c r="AD79" s="12">
         <f t="shared" si="33"/>
-        <v>100</v>
-      </c>
-      <c r="Y79" s="4">
-        <f t="shared" ref="Y79:Y80" si="41">X79</f>
-        <v>100</v>
-      </c>
-      <c r="Z79" s="4"/>
-      <c r="AA79" s="16"/>
-      <c r="AB79" s="16"/>
-      <c r="AC79" s="12">
-        <f t="shared" si="35"/>
-        <v>14.313725490196079</v>
-      </c>
-      <c r="AD79" s="12">
-        <f t="shared" si="32"/>
         <v>4.5098039215686274</v>
       </c>
       <c r="AE79" s="12">
@@ -16060,14 +16272,17 @@
       </c>
       <c r="AO79" s="12"/>
       <c r="AP79" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>35</v>
       </c>
       <c r="AQ79" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR79" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR79" s="12">
+        <f t="shared" si="39"/>
+        <v>3.5699999999999994</v>
+      </c>
       <c r="AS79" s="12"/>
       <c r="AT79" s="12"/>
       <c r="AU79" s="12"/>
@@ -16102,7 +16317,7 @@
         <v>49</v>
       </c>
       <c r="L80" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-49</v>
       </c>
       <c r="M80" s="12"/>
@@ -16121,27 +16336,27 @@
         <v>50</v>
       </c>
       <c r="V80" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="W80" s="4"/>
       <c r="X80" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y80" s="4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Z80" s="4"/>
+      <c r="AA80" s="12"/>
+      <c r="AB80" s="12"/>
+      <c r="AC80" s="12" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD80" s="12" t="e">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y80" s="4">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="Z80" s="4"/>
-      <c r="AA80" s="16"/>
-      <c r="AB80" s="16"/>
-      <c r="AC80" s="12" t="e">
-        <f t="shared" si="35"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD80" s="12" t="e">
-        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE80" s="12">
@@ -16176,14 +16391,17 @@
       </c>
       <c r="AO80" s="12"/>
       <c r="AP80" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ80" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR80" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR80" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS80" s="12"/>
       <c r="AT80" s="12"/>
       <c r="AU80" s="12"/>
@@ -16222,7 +16440,7 @@
         <v>98</v>
       </c>
       <c r="L81" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-2</v>
       </c>
       <c r="M81" s="12"/>
@@ -16237,27 +16455,27 @@
       <c r="T81" s="12"/>
       <c r="U81" s="12"/>
       <c r="V81" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>19.2</v>
       </c>
       <c r="W81" s="4"/>
       <c r="X81" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y81" s="4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z81" s="4"/>
+      <c r="AA81" s="12"/>
+      <c r="AB81" s="12"/>
+      <c r="AC81" s="12">
+        <f t="shared" si="36"/>
+        <v>17.177083333333332</v>
+      </c>
+      <c r="AD81" s="12">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y81" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z81" s="4"/>
-      <c r="AA81" s="16"/>
-      <c r="AB81" s="16"/>
-      <c r="AC81" s="12">
-        <f t="shared" si="35"/>
-        <v>17.177083333333332</v>
-      </c>
-      <c r="AD81" s="12">
-        <f t="shared" si="32"/>
         <v>17.177083333333332</v>
       </c>
       <c r="AE81" s="12">
@@ -16292,14 +16510,17 @@
       </c>
       <c r="AO81" s="12"/>
       <c r="AP81" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ81" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR81" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR81" s="12">
+        <f t="shared" si="39"/>
+        <v>7.68</v>
+      </c>
       <c r="AS81" s="12"/>
       <c r="AT81" s="12"/>
       <c r="AU81" s="12"/>
@@ -16338,7 +16559,7 @@
         <v>19.649999999999999</v>
       </c>
       <c r="L82" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-2.9269999999999996</v>
       </c>
       <c r="M82" s="12"/>
@@ -16353,7 +16574,7 @@
       <c r="T82" s="12"/>
       <c r="U82" s="12"/>
       <c r="V82" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>3.3445999999999998</v>
       </c>
       <c r="W82" s="4">
@@ -16361,22 +16582,22 @@
         <v>18.290599999999998</v>
       </c>
       <c r="X82" s="4">
-        <f t="shared" si="33"/>
-        <v>18.290599999999998</v>
-      </c>
-      <c r="Y82" s="4">
         <f t="shared" si="34"/>
         <v>18.290599999999998</v>
       </c>
+      <c r="Y82" s="4">
+        <f t="shared" si="35"/>
+        <v>18.290599999999998</v>
+      </c>
       <c r="Z82" s="4"/>
-      <c r="AA82" s="16"/>
-      <c r="AB82" s="16"/>
+      <c r="AA82" s="12"/>
+      <c r="AB82" s="12"/>
       <c r="AC82" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11</v>
       </c>
       <c r="AD82" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.5313041918316097</v>
       </c>
       <c r="AE82" s="12">
@@ -16411,14 +16632,17 @@
       </c>
       <c r="AO82" s="12"/>
       <c r="AP82" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>18</v>
       </c>
       <c r="AQ82" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR82" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR82" s="12">
+        <f t="shared" si="39"/>
+        <v>3.3445999999999998</v>
+      </c>
       <c r="AS82" s="12"/>
       <c r="AT82" s="12"/>
       <c r="AU82" s="12"/>
@@ -16457,7 +16681,7 @@
         <v>156.80000000000001</v>
       </c>
       <c r="L83" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-13.493000000000023</v>
       </c>
       <c r="M83" s="12"/>
@@ -16472,27 +16696,27 @@
       <c r="T83" s="12"/>
       <c r="U83" s="12"/>
       <c r="V83" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>28.661399999999997</v>
       </c>
       <c r="W83" s="4"/>
       <c r="X83" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y83" s="4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z83" s="4"/>
+      <c r="AA83" s="12"/>
+      <c r="AB83" s="12"/>
+      <c r="AC83" s="12">
+        <f t="shared" si="36"/>
+        <v>12.50416937065182</v>
+      </c>
+      <c r="AD83" s="12">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y83" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z83" s="4"/>
-      <c r="AA83" s="16"/>
-      <c r="AB83" s="16"/>
-      <c r="AC83" s="12">
-        <f t="shared" si="35"/>
-        <v>12.50416937065182</v>
-      </c>
-      <c r="AD83" s="12">
-        <f t="shared" si="32"/>
         <v>12.50416937065182</v>
       </c>
       <c r="AE83" s="12">
@@ -16527,14 +16751,17 @@
       </c>
       <c r="AO83" s="12"/>
       <c r="AP83" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ83" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR83" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR83" s="12">
+        <f t="shared" si="39"/>
+        <v>28.661399999999997</v>
+      </c>
       <c r="AS83" s="12"/>
       <c r="AT83" s="12"/>
       <c r="AU83" s="12"/>
@@ -16573,7 +16800,7 @@
         <v>808.06</v>
       </c>
       <c r="L84" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-4.8000000000001819E-2</v>
       </c>
       <c r="M84" s="12"/>
@@ -16592,7 +16819,7 @@
         <v>336.6</v>
       </c>
       <c r="V84" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>161.60239999999999</v>
       </c>
       <c r="W84" s="4">
@@ -16604,21 +16831,21 @@
         <v>385.98667611679969</v>
       </c>
       <c r="Y84" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>217.31049865375823</v>
       </c>
       <c r="Z84" s="4">
         <f>X84*$Z$1</f>
         <v>168.67617746304145</v>
       </c>
-      <c r="AA84" s="16"/>
-      <c r="AB84" s="16"/>
+      <c r="AA84" s="12"/>
+      <c r="AB84" s="12"/>
       <c r="AC84" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.864999999999998</v>
       </c>
       <c r="AD84" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.476504061098105</v>
       </c>
       <c r="AE84" s="12">
@@ -16653,14 +16880,17 @@
       </c>
       <c r="AO84" s="12"/>
       <c r="AP84" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>217</v>
       </c>
       <c r="AQ84" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>169</v>
       </c>
-      <c r="AR84" s="12"/>
+      <c r="AR84" s="12">
+        <f t="shared" si="39"/>
+        <v>161.60239999999999</v>
+      </c>
       <c r="AS84" s="12"/>
       <c r="AT84" s="12"/>
       <c r="AU84" s="12"/>
@@ -16687,7 +16917,7 @@
       <c r="J85" s="8"/>
       <c r="K85" s="8"/>
       <c r="L85" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M85" s="8"/>
@@ -16702,27 +16932,27 @@
       <c r="T85" s="8"/>
       <c r="U85" s="8"/>
       <c r="V85" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="W85" s="10"/>
       <c r="X85" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y85" s="4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z85" s="4"/>
+      <c r="AA85" s="12"/>
+      <c r="AB85" s="12"/>
+      <c r="AC85" s="12" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD85" s="8" t="e">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y85" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z85" s="4"/>
-      <c r="AA85" s="16"/>
-      <c r="AB85" s="16"/>
-      <c r="AC85" s="12" t="e">
-        <f t="shared" si="35"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD85" s="8" t="e">
-        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE85" s="8">
@@ -16759,14 +16989,17 @@
         <v>46</v>
       </c>
       <c r="AP85" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ85" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR85" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR85" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS85" s="12"/>
       <c r="AT85" s="12"/>
       <c r="AU85" s="12"/>
@@ -16805,7 +17038,7 @@
         <v>2900.3</v>
       </c>
       <c r="L86" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.72100000000000364</v>
       </c>
       <c r="M86" s="12"/>
@@ -16826,33 +17059,33 @@
         <v>1431.0884988</v>
       </c>
       <c r="V86" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>580.20420000000001</v>
       </c>
       <c r="W86" s="4">
-        <f t="shared" ref="W86:W88" si="42">10*V86-U86-T86-S86-R86-Q86-P86-O86-F86</f>
+        <f t="shared" ref="W86:W88" si="44">10*V86-U86-T86-S86-R86-Q86-P86-O86-F86</f>
         <v>348.00541999999996</v>
       </c>
       <c r="X86" s="4">
-        <f t="shared" ref="X86:X88" si="43">W86+V86*$X$1</f>
+        <f t="shared" ref="X86:X88" si="45">W86+V86*$X$1</f>
         <v>1430.0862529999999</v>
       </c>
       <c r="Y86" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>805.138560439</v>
       </c>
       <c r="Z86" s="4">
-        <f t="shared" ref="Z86:Z88" si="44">X86*$Z$1</f>
+        <f t="shared" ref="Z86:Z88" si="46">X86*$Z$1</f>
         <v>624.94769256099994</v>
       </c>
-      <c r="AA86" s="16"/>
-      <c r="AB86" s="16"/>
+      <c r="AA86" s="12"/>
+      <c r="AB86" s="12"/>
       <c r="AC86" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.864999999999998</v>
       </c>
       <c r="AD86" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>9.4002018254952304</v>
       </c>
       <c r="AE86" s="12">
@@ -16887,14 +17120,17 @@
       </c>
       <c r="AO86" s="12"/>
       <c r="AP86" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>805</v>
       </c>
       <c r="AQ86" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>625</v>
       </c>
-      <c r="AR86" s="12"/>
+      <c r="AR86" s="12">
+        <f t="shared" si="39"/>
+        <v>580.20420000000001</v>
+      </c>
       <c r="AS86" s="12"/>
       <c r="AT86" s="12"/>
       <c r="AU86" s="12"/>
@@ -16933,7 +17169,7 @@
         <v>2818.1</v>
       </c>
       <c r="L87" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4.2159999999998945</v>
       </c>
       <c r="M87" s="12"/>
@@ -16952,33 +17188,33 @@
         <v>1213.9602623999999</v>
       </c>
       <c r="V87" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>564.46319999999992</v>
       </c>
       <c r="W87" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1384.0097999999996</v>
       </c>
       <c r="X87" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>2436.7336679999994</v>
       </c>
       <c r="Y87" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1371.8810550839996</v>
       </c>
       <c r="Z87" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>1064.8526129159998</v>
       </c>
-      <c r="AA87" s="16"/>
-      <c r="AB87" s="16"/>
+      <c r="AA87" s="12"/>
+      <c r="AB87" s="12"/>
       <c r="AC87" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.865000000000002</v>
       </c>
       <c r="AD87" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.5480956065869318</v>
       </c>
       <c r="AE87" s="12">
@@ -17013,14 +17249,17 @@
       </c>
       <c r="AO87" s="12"/>
       <c r="AP87" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1372</v>
       </c>
       <c r="AQ87" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1065</v>
       </c>
-      <c r="AR87" s="12"/>
+      <c r="AR87" s="12">
+        <f t="shared" si="39"/>
+        <v>564.46319999999992</v>
+      </c>
       <c r="AS87" s="12"/>
       <c r="AT87" s="12"/>
       <c r="AU87" s="12"/>
@@ -17059,7 +17298,7 @@
         <v>2946.6</v>
       </c>
       <c r="L88" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-10.632999999999811</v>
       </c>
       <c r="M88" s="12"/>
@@ -17078,33 +17317,33 @@
         <v>1420.4994300000001</v>
       </c>
       <c r="V88" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>587.1934</v>
       </c>
       <c r="W88" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>100.19014000000107</v>
       </c>
       <c r="X88" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>1195.305831000001</v>
       </c>
       <c r="Y88" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>672.95718285300063</v>
       </c>
       <c r="Z88" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>522.3486481470004</v>
       </c>
-      <c r="AA88" s="16"/>
-      <c r="AB88" s="16"/>
+      <c r="AA88" s="12"/>
+      <c r="AB88" s="12"/>
       <c r="AC88" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.865</v>
       </c>
       <c r="AD88" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>9.8293745467847558</v>
       </c>
       <c r="AE88" s="12">
@@ -17139,14 +17378,17 @@
       </c>
       <c r="AO88" s="12"/>
       <c r="AP88" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>673</v>
       </c>
       <c r="AQ88" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>522</v>
       </c>
-      <c r="AR88" s="12"/>
+      <c r="AR88" s="12">
+        <f t="shared" si="39"/>
+        <v>587.1934</v>
+      </c>
       <c r="AS88" s="12"/>
       <c r="AT88" s="12"/>
       <c r="AU88" s="12"/>
@@ -17185,7 +17427,7 @@
         <v>42.6</v>
       </c>
       <c r="L89" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-2.3890000000000029</v>
       </c>
       <c r="M89" s="12"/>
@@ -17200,7 +17442,7 @@
       <c r="T89" s="12"/>
       <c r="U89" s="12"/>
       <c r="V89" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>8.0421999999999993</v>
       </c>
       <c r="W89" s="4">
@@ -17208,22 +17450,22 @@
         <v>47.567199999999993</v>
       </c>
       <c r="X89" s="4">
-        <f t="shared" si="33"/>
-        <v>47.567199999999993</v>
-      </c>
-      <c r="Y89" s="4">
         <f t="shared" si="34"/>
         <v>47.567199999999993</v>
       </c>
+      <c r="Y89" s="4">
+        <f t="shared" si="35"/>
+        <v>47.567199999999993</v>
+      </c>
       <c r="Z89" s="4"/>
-      <c r="AA89" s="16"/>
-      <c r="AB89" s="16"/>
+      <c r="AA89" s="12"/>
+      <c r="AB89" s="12"/>
       <c r="AC89" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11</v>
       </c>
       <c r="AD89" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.0853000422769892</v>
       </c>
       <c r="AE89" s="12">
@@ -17258,14 +17500,17 @@
       </c>
       <c r="AO89" s="12"/>
       <c r="AP89" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>48</v>
       </c>
       <c r="AQ89" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR89" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR89" s="12">
+        <f t="shared" si="39"/>
+        <v>8.0421999999999993</v>
+      </c>
       <c r="AS89" s="12"/>
       <c r="AT89" s="12"/>
       <c r="AU89" s="12"/>
@@ -17298,7 +17543,7 @@
         <v>2</v>
       </c>
       <c r="L90" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-12</v>
       </c>
       <c r="M90" s="12"/>
@@ -17315,12 +17560,12 @@
         <v>40</v>
       </c>
       <c r="V90" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-2</v>
       </c>
       <c r="W90" s="4"/>
       <c r="X90" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y90" s="4">
@@ -17328,14 +17573,14 @@
         <v>0</v>
       </c>
       <c r="Z90" s="4"/>
-      <c r="AA90" s="16"/>
-      <c r="AB90" s="16"/>
+      <c r="AA90" s="12"/>
+      <c r="AB90" s="12"/>
       <c r="AC90" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-40</v>
       </c>
       <c r="AD90" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-40</v>
       </c>
       <c r="AE90" s="12">
@@ -17370,14 +17615,17 @@
       </c>
       <c r="AO90" s="12"/>
       <c r="AP90" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ90" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR90" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR90" s="12">
+        <f t="shared" si="39"/>
+        <v>-0.6</v>
+      </c>
       <c r="AS90" s="12"/>
       <c r="AT90" s="12"/>
       <c r="AU90" s="12"/>
@@ -17416,7 +17664,7 @@
         <v>53</v>
       </c>
       <c r="L91" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-6</v>
       </c>
       <c r="M91" s="12"/>
@@ -17433,27 +17681,27 @@
       <c r="T91" s="12"/>
       <c r="U91" s="12"/>
       <c r="V91" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9.4</v>
       </c>
       <c r="W91" s="4"/>
       <c r="X91" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y91" s="4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z91" s="4"/>
+      <c r="AA91" s="12"/>
+      <c r="AB91" s="12"/>
+      <c r="AC91" s="12">
+        <f t="shared" si="36"/>
+        <v>73.944680851063836</v>
+      </c>
+      <c r="AD91" s="12">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y91" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z91" s="4"/>
-      <c r="AA91" s="16"/>
-      <c r="AB91" s="16"/>
-      <c r="AC91" s="12">
-        <f t="shared" si="35"/>
-        <v>73.944680851063836</v>
-      </c>
-      <c r="AD91" s="12">
-        <f t="shared" si="32"/>
         <v>73.944680851063836</v>
       </c>
       <c r="AE91" s="12">
@@ -17490,14 +17738,17 @@
         <v>110</v>
       </c>
       <c r="AP91" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ91" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR91" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR91" s="12">
+        <f t="shared" si="39"/>
+        <v>2.82</v>
+      </c>
       <c r="AS91" s="12"/>
       <c r="AT91" s="12"/>
       <c r="AU91" s="12"/>
@@ -17526,7 +17777,7 @@
         <v>3</v>
       </c>
       <c r="L92" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-3</v>
       </c>
       <c r="M92" s="8"/>
@@ -17541,27 +17792,27 @@
       <c r="T92" s="8"/>
       <c r="U92" s="8"/>
       <c r="V92" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="W92" s="10"/>
       <c r="X92" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y92" s="4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z92" s="4"/>
+      <c r="AA92" s="12"/>
+      <c r="AB92" s="12"/>
+      <c r="AC92" s="12" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD92" s="8" t="e">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y92" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z92" s="4"/>
-      <c r="AA92" s="16"/>
-      <c r="AB92" s="16"/>
-      <c r="AC92" s="12" t="e">
-        <f t="shared" si="35"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD92" s="8" t="e">
-        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE92" s="8">
@@ -17598,14 +17849,17 @@
         <v>46</v>
       </c>
       <c r="AP92" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ92" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR92" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR92" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS92" s="12"/>
       <c r="AT92" s="12"/>
       <c r="AU92" s="12"/>
@@ -17644,7 +17898,7 @@
         <v>140</v>
       </c>
       <c r="L93" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1</v>
       </c>
       <c r="M93" s="12"/>
@@ -17661,27 +17915,27 @@
         <v>30</v>
       </c>
       <c r="V93" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>27.8</v>
       </c>
       <c r="W93" s="4"/>
       <c r="X93" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y93" s="4">
+        <f t="shared" ref="Y93:Y94" si="47">X93</f>
+        <v>0</v>
+      </c>
+      <c r="Z93" s="4"/>
+      <c r="AA93" s="12"/>
+      <c r="AB93" s="12"/>
+      <c r="AC93" s="12">
+        <f t="shared" si="36"/>
+        <v>13.381294964028777</v>
+      </c>
+      <c r="AD93" s="12">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y93" s="4">
-        <f t="shared" ref="Y93:Y94" si="45">X93</f>
-        <v>0</v>
-      </c>
-      <c r="Z93" s="4"/>
-      <c r="AA93" s="16"/>
-      <c r="AB93" s="16"/>
-      <c r="AC93" s="12">
-        <f t="shared" si="35"/>
-        <v>13.381294964028777</v>
-      </c>
-      <c r="AD93" s="12">
-        <f t="shared" si="32"/>
         <v>13.381294964028777</v>
       </c>
       <c r="AE93" s="12">
@@ -17716,14 +17970,17 @@
       </c>
       <c r="AO93" s="12"/>
       <c r="AP93" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ93" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR93" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR93" s="12">
+        <f t="shared" si="39"/>
+        <v>1.9460000000000002</v>
+      </c>
       <c r="AS93" s="12"/>
       <c r="AT93" s="12"/>
       <c r="AU93" s="12"/>
@@ -17762,7 +18019,7 @@
         <v>134</v>
       </c>
       <c r="L94" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-2</v>
       </c>
       <c r="M94" s="12"/>
@@ -17783,29 +18040,29 @@
         <v>40</v>
       </c>
       <c r="V94" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>26.4</v>
       </c>
       <c r="W94" s="4">
         <v>50</v>
       </c>
       <c r="X94" s="4">
+        <f t="shared" si="34"/>
+        <v>50</v>
+      </c>
+      <c r="Y94" s="4">
+        <f t="shared" si="47"/>
+        <v>50</v>
+      </c>
+      <c r="Z94" s="4"/>
+      <c r="AA94" s="12"/>
+      <c r="AB94" s="12"/>
+      <c r="AC94" s="12">
+        <f t="shared" si="36"/>
+        <v>13.742424242424242</v>
+      </c>
+      <c r="AD94" s="12">
         <f t="shared" si="33"/>
-        <v>50</v>
-      </c>
-      <c r="Y94" s="4">
-        <f t="shared" si="45"/>
-        <v>50</v>
-      </c>
-      <c r="Z94" s="4"/>
-      <c r="AA94" s="16"/>
-      <c r="AB94" s="16"/>
-      <c r="AC94" s="12">
-        <f t="shared" si="35"/>
-        <v>13.742424242424242</v>
-      </c>
-      <c r="AD94" s="12">
-        <f t="shared" si="32"/>
         <v>11.848484848484848</v>
       </c>
       <c r="AE94" s="12">
@@ -17840,14 +18097,17 @@
       </c>
       <c r="AO94" s="12"/>
       <c r="AP94" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4</v>
       </c>
       <c r="AQ94" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR94" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR94" s="12">
+        <f t="shared" si="39"/>
+        <v>1.8480000000000001</v>
+      </c>
       <c r="AS94" s="12"/>
       <c r="AT94" s="12"/>
       <c r="AU94" s="12"/>
@@ -17886,7 +18146,7 @@
         <v>119</v>
       </c>
       <c r="L95" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-3</v>
       </c>
       <c r="M95" s="12"/>
@@ -17901,27 +18161,27 @@
       <c r="T95" s="12"/>
       <c r="U95" s="12"/>
       <c r="V95" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>23.2</v>
       </c>
       <c r="W95" s="4"/>
       <c r="X95" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y95" s="4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z95" s="4"/>
+      <c r="AA95" s="12"/>
+      <c r="AB95" s="12"/>
+      <c r="AC95" s="12">
+        <f t="shared" si="36"/>
+        <v>12.875</v>
+      </c>
+      <c r="AD95" s="12">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y95" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z95" s="4"/>
-      <c r="AA95" s="16"/>
-      <c r="AB95" s="16"/>
-      <c r="AC95" s="12">
-        <f t="shared" si="35"/>
-        <v>12.875</v>
-      </c>
-      <c r="AD95" s="12">
-        <f t="shared" si="32"/>
         <v>12.875</v>
       </c>
       <c r="AE95" s="12">
@@ -17956,14 +18216,17 @@
       </c>
       <c r="AO95" s="12"/>
       <c r="AP95" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ95" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR95" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR95" s="12">
+        <f t="shared" si="39"/>
+        <v>6.96</v>
+      </c>
       <c r="AS95" s="12"/>
       <c r="AT95" s="12"/>
       <c r="AU95" s="12"/>
@@ -18002,7 +18265,7 @@
         <v>88.5</v>
       </c>
       <c r="L96" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.3340000000000032</v>
       </c>
       <c r="M96" s="12"/>
@@ -18019,12 +18282,12 @@
         <v>40</v>
       </c>
       <c r="V96" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>19.166800000000002</v>
       </c>
       <c r="W96" s="4"/>
       <c r="X96" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y96" s="4">
@@ -18032,14 +18295,14 @@
         <v>0</v>
       </c>
       <c r="Z96" s="4"/>
-      <c r="AA96" s="16"/>
-      <c r="AB96" s="16"/>
+      <c r="AA96" s="12"/>
+      <c r="AB96" s="12"/>
       <c r="AC96" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.487420957071601</v>
       </c>
       <c r="AD96" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>11.487420957071601</v>
       </c>
       <c r="AE96" s="12">
@@ -18074,14 +18337,17 @@
       </c>
       <c r="AO96" s="12"/>
       <c r="AP96" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ96" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR96" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR96" s="12">
+        <f t="shared" si="39"/>
+        <v>19.166800000000002</v>
+      </c>
       <c r="AS96" s="12"/>
       <c r="AT96" s="12"/>
       <c r="AU96" s="12"/>
@@ -18108,7 +18374,7 @@
       <c r="J97" s="8"/>
       <c r="K97" s="8"/>
       <c r="L97" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M97" s="8"/>
@@ -18123,27 +18389,27 @@
       <c r="T97" s="8"/>
       <c r="U97" s="8"/>
       <c r="V97" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="W97" s="10"/>
       <c r="X97" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y97" s="4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z97" s="4"/>
+      <c r="AA97" s="12"/>
+      <c r="AB97" s="12"/>
+      <c r="AC97" s="12" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD97" s="8" t="e">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y97" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z97" s="4"/>
-      <c r="AA97" s="16"/>
-      <c r="AB97" s="16"/>
-      <c r="AC97" s="12" t="e">
-        <f t="shared" si="35"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD97" s="8" t="e">
-        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE97" s="8">
@@ -18180,14 +18446,17 @@
         <v>46</v>
       </c>
       <c r="AP97" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ97" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR97" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR97" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS97" s="12"/>
       <c r="AT97" s="12"/>
       <c r="AU97" s="12"/>
@@ -18216,7 +18485,7 @@
       <c r="J98" s="12"/>
       <c r="K98" s="12"/>
       <c r="L98" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M98" s="12"/>
@@ -18235,14 +18504,14 @@
         <v>10</v>
       </c>
       <c r="V98" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="W98" s="4">
         <v>10</v>
       </c>
       <c r="X98" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10</v>
       </c>
       <c r="Y98" s="4">
@@ -18250,14 +18519,14 @@
         <v>10</v>
       </c>
       <c r="Z98" s="4"/>
-      <c r="AA98" s="16"/>
-      <c r="AB98" s="16"/>
+      <c r="AA98" s="12"/>
+      <c r="AB98" s="12"/>
       <c r="AC98" s="12" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD98" s="12" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE98" s="12">
@@ -18294,14 +18563,17 @@
         <v>141</v>
       </c>
       <c r="AP98" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="AQ98" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR98" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR98" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS98" s="12"/>
       <c r="AT98" s="12"/>
       <c r="AU98" s="12"/>
@@ -18340,7 +18612,7 @@
         <v>273</v>
       </c>
       <c r="L99" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-15</v>
       </c>
       <c r="M99" s="12"/>
@@ -18355,7 +18627,7 @@
       <c r="T99" s="12"/>
       <c r="U99" s="12"/>
       <c r="V99" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>51.6</v>
       </c>
       <c r="W99" s="4"/>
@@ -18364,18 +18636,18 @@
         <v>96.234000000000009</v>
       </c>
       <c r="Y99" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>96.234000000000009</v>
       </c>
       <c r="Z99" s="4"/>
-      <c r="AA99" s="16"/>
-      <c r="AB99" s="16"/>
+      <c r="AA99" s="12"/>
+      <c r="AB99" s="12"/>
       <c r="AC99" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>13.318488372093023</v>
       </c>
       <c r="AD99" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>11.453488372093023</v>
       </c>
       <c r="AE99" s="12">
@@ -18410,14 +18682,17 @@
       </c>
       <c r="AO99" s="12"/>
       <c r="AP99" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>8</v>
       </c>
       <c r="AQ99" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR99" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR99" s="12">
+        <f t="shared" si="39"/>
+        <v>4.1280000000000001</v>
+      </c>
       <c r="AS99" s="12"/>
       <c r="AT99" s="12"/>
       <c r="AU99" s="12"/>
@@ -18456,7 +18731,7 @@
         <v>225</v>
       </c>
       <c r="L100" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-14</v>
       </c>
       <c r="M100" s="12"/>
@@ -18471,27 +18746,27 @@
       <c r="T100" s="12"/>
       <c r="U100" s="12"/>
       <c r="V100" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>42.2</v>
       </c>
       <c r="W100" s="4"/>
       <c r="X100" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y100" s="4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z100" s="4"/>
+      <c r="AA100" s="12"/>
+      <c r="AB100" s="12"/>
+      <c r="AC100" s="12">
+        <f t="shared" si="36"/>
+        <v>12.180094786729857</v>
+      </c>
+      <c r="AD100" s="12">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y100" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z100" s="4"/>
-      <c r="AA100" s="16"/>
-      <c r="AB100" s="16"/>
-      <c r="AC100" s="12">
-        <f t="shared" si="35"/>
-        <v>12.180094786729857</v>
-      </c>
-      <c r="AD100" s="12">
-        <f t="shared" si="32"/>
         <v>12.180094786729857</v>
       </c>
       <c r="AE100" s="12">
@@ -18526,14 +18801,17 @@
       </c>
       <c r="AO100" s="12"/>
       <c r="AP100" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ100" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR100" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR100" s="12">
+        <f t="shared" si="39"/>
+        <v>3.3760000000000003</v>
+      </c>
       <c r="AS100" s="12"/>
       <c r="AT100" s="12"/>
       <c r="AU100" s="12"/>
@@ -18572,7 +18850,7 @@
         <v>6</v>
       </c>
       <c r="L101" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M101" s="12"/>
@@ -18587,27 +18865,27 @@
       <c r="T101" s="12"/>
       <c r="U101" s="12"/>
       <c r="V101" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1.2</v>
       </c>
       <c r="W101" s="4"/>
       <c r="X101" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Y101" s="4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z101" s="4"/>
+      <c r="AA101" s="12"/>
+      <c r="AB101" s="12"/>
+      <c r="AC101" s="12">
+        <f t="shared" si="36"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AD101" s="12">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="Y101" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z101" s="4"/>
-      <c r="AA101" s="16"/>
-      <c r="AB101" s="16"/>
-      <c r="AC101" s="12">
-        <f t="shared" si="35"/>
-        <v>21.666666666666668</v>
-      </c>
-      <c r="AD101" s="12">
-        <f t="shared" si="32"/>
         <v>21.666666666666668</v>
       </c>
       <c r="AE101" s="12">
@@ -18644,14 +18922,17 @@
         <v>145</v>
       </c>
       <c r="AP101" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ101" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR101" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR101" s="12">
+        <f t="shared" si="39"/>
+        <v>0.20400000000000001</v>
+      </c>
       <c r="AS101" s="12"/>
       <c r="AT101" s="12"/>
       <c r="AU101" s="12"/>
@@ -18690,7 +18971,7 @@
         <v>678.8</v>
       </c>
       <c r="L102" s="12">
-        <f t="shared" ref="L102:L129" si="46">E102-K102</f>
+        <f t="shared" ref="L102:L129" si="48">E102-K102</f>
         <v>-243.57499999999993</v>
       </c>
       <c r="M102" s="12"/>
@@ -18707,35 +18988,35 @@
         <v>50</v>
       </c>
       <c r="V102" s="12">
-        <f t="shared" ref="V102:V129" si="47">E102/5</f>
+        <f t="shared" ref="V102:V129" si="49">E102/5</f>
         <v>87.045000000000002</v>
       </c>
       <c r="W102" s="4">
         <v>300</v>
       </c>
       <c r="X102" s="4">
-        <f t="shared" ref="X102:X104" si="48">AA102</f>
+        <f t="shared" ref="X102:X104" si="50">AA102</f>
         <v>400</v>
       </c>
       <c r="Y102" s="4">
-        <f t="shared" ref="Y102:Y104" si="49">X102</f>
+        <f t="shared" ref="Y102:Y104" si="51">X102</f>
         <v>400</v>
       </c>
       <c r="Z102" s="4"/>
-      <c r="AA102" s="16">
+      <c r="AA102" s="12">
         <f>VLOOKUP(A102,[1]Sheet!$A:$Y,24,0)</f>
         <v>400</v>
       </c>
-      <c r="AB102" s="16" t="str">
+      <c r="AB102" s="12" t="str">
         <f>VLOOKUP(A102,[1]Sheet!$A:$Y,25,0)</f>
         <v>промо жц</v>
       </c>
       <c r="AC102" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.8846918260669767</v>
       </c>
       <c r="AD102" s="12">
-        <f t="shared" ref="AD102:AD129" si="50">(F102+O102+P102+Q102+R102+S102+T102+U102)/V102</f>
+        <f t="shared" ref="AD102:AD129" si="52">(F102+O102+P102+Q102+R102+S102+T102+U102)/V102</f>
         <v>2.2893675684990522</v>
       </c>
       <c r="AE102" s="12">
@@ -18772,14 +19053,17 @@
         <v>62</v>
       </c>
       <c r="AP102" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>400</v>
       </c>
       <c r="AQ102" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR102" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR102" s="12">
+        <f t="shared" si="39"/>
+        <v>87.045000000000002</v>
+      </c>
       <c r="AS102" s="12"/>
       <c r="AT102" s="12"/>
       <c r="AU102" s="12"/>
@@ -18818,7 +19102,7 @@
         <v>692.1</v>
       </c>
       <c r="L103" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-83.572000000000003</v>
       </c>
       <c r="M103" s="12"/>
@@ -18833,35 +19117,35 @@
       <c r="T103" s="12"/>
       <c r="U103" s="12"/>
       <c r="V103" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>121.7056</v>
       </c>
       <c r="W103" s="4">
         <v>600</v>
       </c>
       <c r="X103" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>700</v>
       </c>
       <c r="Y103" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>700</v>
       </c>
       <c r="Z103" s="4"/>
-      <c r="AA103" s="16">
+      <c r="AA103" s="12">
         <f>VLOOKUP(A103,[1]Sheet!$A:$Y,24,0)</f>
         <v>700</v>
       </c>
-      <c r="AB103" s="16" t="str">
+      <c r="AB103" s="12" t="str">
         <f>VLOOKUP(A103,[1]Sheet!$A:$Y,25,0)</f>
         <v>промо жц</v>
       </c>
       <c r="AC103" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>7.2079263402834375</v>
       </c>
       <c r="AD103" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>1.4563421896773854</v>
       </c>
       <c r="AE103" s="12">
@@ -18898,14 +19182,17 @@
         <v>62</v>
       </c>
       <c r="AP103" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>700</v>
       </c>
       <c r="AQ103" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR103" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR103" s="12">
+        <f t="shared" si="39"/>
+        <v>121.7056</v>
+      </c>
       <c r="AS103" s="12"/>
       <c r="AT103" s="12"/>
       <c r="AU103" s="12"/>
@@ -18938,7 +19225,7 @@
         <v>166.1</v>
       </c>
       <c r="L104" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-175.547</v>
       </c>
       <c r="M104" s="12"/>
@@ -18957,35 +19244,35 @@
         <v>100</v>
       </c>
       <c r="V104" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1.8893999999999997</v>
       </c>
       <c r="W104" s="4">
         <v>150</v>
       </c>
       <c r="X104" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>200</v>
       </c>
       <c r="Y104" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>200</v>
       </c>
       <c r="Z104" s="4"/>
-      <c r="AA104" s="16">
+      <c r="AA104" s="12">
         <f>VLOOKUP(A104,[1]Sheet!$A:$Y,24,0)</f>
         <v>200</v>
       </c>
-      <c r="AB104" s="16" t="str">
+      <c r="AB104" s="12" t="str">
         <f>VLOOKUP(A104,[1]Sheet!$A:$Y,25,0)</f>
         <v>промо жц</v>
       </c>
       <c r="AC104" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-158.515930983381</v>
       </c>
       <c r="AD104" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>-52.662220810839429</v>
       </c>
       <c r="AE104" s="12">
@@ -19020,14 +19307,17 @@
       </c>
       <c r="AO104" s="12"/>
       <c r="AP104" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>200</v>
       </c>
       <c r="AQ104" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR104" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR104" s="12">
+        <f t="shared" si="39"/>
+        <v>-1.8893999999999997</v>
+      </c>
       <c r="AS104" s="12"/>
       <c r="AT104" s="12"/>
       <c r="AU104" s="12"/>
@@ -19054,7 +19344,7 @@
       <c r="J105" s="8"/>
       <c r="K105" s="8"/>
       <c r="L105" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M105" s="8"/>
@@ -19069,27 +19359,27 @@
       <c r="T105" s="8"/>
       <c r="U105" s="8"/>
       <c r="V105" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="W105" s="10"/>
       <c r="X105" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y105" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z105" s="4"/>
-      <c r="AA105" s="16"/>
-      <c r="AB105" s="16"/>
+      <c r="AA105" s="12"/>
+      <c r="AB105" s="12"/>
       <c r="AC105" s="12" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD105" s="8" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE105" s="8">
@@ -19126,14 +19416,17 @@
         <v>46</v>
       </c>
       <c r="AP105" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ105" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR105" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR105" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS105" s="12"/>
       <c r="AT105" s="12"/>
       <c r="AU105" s="12"/>
@@ -19172,7 +19465,7 @@
         <v>20.5</v>
       </c>
       <c r="L106" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>2.6799999999999997</v>
       </c>
       <c r="M106" s="12"/>
@@ -19187,7 +19480,7 @@
       <c r="T106" s="12"/>
       <c r="U106" s="12"/>
       <c r="V106" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>4.6360000000000001</v>
       </c>
       <c r="W106" s="4">
@@ -19195,22 +19488,22 @@
         <v>27.532999999999998</v>
       </c>
       <c r="X106" s="4">
-        <f t="shared" si="33"/>
-        <v>27.532999999999998</v>
-      </c>
-      <c r="Y106" s="4">
         <f t="shared" si="34"/>
         <v>27.532999999999998</v>
       </c>
+      <c r="Y106" s="4">
+        <f t="shared" si="35"/>
+        <v>27.532999999999998</v>
+      </c>
       <c r="Z106" s="4"/>
-      <c r="AA106" s="16"/>
-      <c r="AB106" s="16"/>
+      <c r="AA106" s="12"/>
+      <c r="AB106" s="12"/>
       <c r="AC106" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>10</v>
       </c>
       <c r="AD106" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>4.0610440034512516</v>
       </c>
       <c r="AE106" s="12">
@@ -19247,14 +19540,17 @@
         <v>151</v>
       </c>
       <c r="AP106" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>28</v>
       </c>
       <c r="AQ106" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR106" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR106" s="12">
+        <f t="shared" si="39"/>
+        <v>4.6360000000000001</v>
+      </c>
       <c r="AS106" s="12"/>
       <c r="AT106" s="12"/>
       <c r="AU106" s="12"/>
@@ -19293,7 +19589,7 @@
         <v>664</v>
       </c>
       <c r="L107" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-499</v>
       </c>
       <c r="M107" s="12"/>
@@ -19310,14 +19606,14 @@
         <v>50</v>
       </c>
       <c r="V107" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>33</v>
       </c>
       <c r="W107" s="4">
         <v>200</v>
       </c>
       <c r="X107" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>200</v>
       </c>
       <c r="Y107" s="4">
@@ -19328,14 +19624,14 @@
         <f>0.5*X107</f>
         <v>100</v>
       </c>
-      <c r="AA107" s="16"/>
-      <c r="AB107" s="16"/>
+      <c r="AA107" s="12"/>
+      <c r="AB107" s="12"/>
       <c r="AC107" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>27.818181818181817</v>
       </c>
       <c r="AD107" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>18.727272727272727</v>
       </c>
       <c r="AE107" s="12">
@@ -19370,14 +19666,17 @@
       </c>
       <c r="AO107" s="12"/>
       <c r="AP107" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>56</v>
       </c>
       <c r="AQ107" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>28</v>
       </c>
-      <c r="AR107" s="12"/>
+      <c r="AR107" s="12">
+        <f t="shared" si="39"/>
+        <v>9.24</v>
+      </c>
       <c r="AS107" s="12"/>
       <c r="AT107" s="12"/>
       <c r="AU107" s="12"/>
@@ -19404,7 +19703,7 @@
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
       <c r="L108" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M108" s="8"/>
@@ -19419,27 +19718,27 @@
       <c r="T108" s="8"/>
       <c r="U108" s="8"/>
       <c r="V108" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="W108" s="10"/>
       <c r="X108" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y108" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z108" s="4"/>
-      <c r="AA108" s="16"/>
-      <c r="AB108" s="16"/>
+      <c r="AA108" s="12"/>
+      <c r="AB108" s="12"/>
       <c r="AC108" s="12" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD108" s="8" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE108" s="8">
@@ -19476,14 +19775,17 @@
         <v>46</v>
       </c>
       <c r="AP108" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ108" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR108" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR108" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS108" s="12"/>
       <c r="AT108" s="12"/>
       <c r="AU108" s="12"/>
@@ -19522,7 +19824,7 @@
         <v>670</v>
       </c>
       <c r="L109" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-613</v>
       </c>
       <c r="M109" s="12"/>
@@ -19539,14 +19841,14 @@
         <v>100</v>
       </c>
       <c r="V109" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>11.4</v>
       </c>
       <c r="W109" s="4">
         <v>100</v>
       </c>
       <c r="X109" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>100</v>
       </c>
       <c r="Y109" s="4">
@@ -19554,14 +19856,14 @@
         <v>100</v>
       </c>
       <c r="Z109" s="4"/>
-      <c r="AA109" s="16"/>
-      <c r="AB109" s="16"/>
+      <c r="AA109" s="12"/>
+      <c r="AB109" s="12"/>
       <c r="AC109" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>37.192982456140349</v>
       </c>
       <c r="AD109" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>28.421052631578945</v>
       </c>
       <c r="AE109" s="12">
@@ -19596,14 +19898,17 @@
       </c>
       <c r="AO109" s="12"/>
       <c r="AP109" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>28</v>
       </c>
       <c r="AQ109" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR109" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR109" s="12">
+        <f t="shared" si="39"/>
+        <v>3.1920000000000006</v>
+      </c>
       <c r="AS109" s="12"/>
       <c r="AT109" s="12"/>
       <c r="AU109" s="12"/>
@@ -19640,7 +19945,7 @@
         <v>131</v>
       </c>
       <c r="L110" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-11</v>
       </c>
       <c r="M110" s="12"/>
@@ -19655,7 +19960,7 @@
       <c r="T110" s="12"/>
       <c r="U110" s="12"/>
       <c r="V110" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>24</v>
       </c>
       <c r="W110" s="4">
@@ -19663,22 +19968,22 @@
         <v>60.199999999999989</v>
       </c>
       <c r="X110" s="4">
-        <f t="shared" si="33"/>
-        <v>60.199999999999989</v>
-      </c>
-      <c r="Y110" s="4">
         <f t="shared" si="34"/>
         <v>60.199999999999989</v>
       </c>
+      <c r="Y110" s="4">
+        <f t="shared" si="35"/>
+        <v>60.199999999999989</v>
+      </c>
       <c r="Z110" s="4"/>
-      <c r="AA110" s="16"/>
-      <c r="AB110" s="16"/>
+      <c r="AA110" s="12"/>
+      <c r="AB110" s="12"/>
       <c r="AC110" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11</v>
       </c>
       <c r="AD110" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>8.4916666666666671</v>
       </c>
       <c r="AE110" s="12">
@@ -19713,14 +20018,17 @@
       </c>
       <c r="AO110" s="12"/>
       <c r="AP110" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5</v>
       </c>
       <c r="AQ110" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR110" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR110" s="12">
+        <f t="shared" si="39"/>
+        <v>2.16</v>
+      </c>
       <c r="AS110" s="12"/>
       <c r="AT110" s="12"/>
       <c r="AU110" s="12"/>
@@ -19757,7 +20065,7 @@
         <v>100</v>
       </c>
       <c r="L111" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-2.4579999999999984</v>
       </c>
       <c r="M111" s="12"/>
@@ -19772,27 +20080,27 @@
       <c r="T111" s="12"/>
       <c r="U111" s="12"/>
       <c r="V111" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>19.508400000000002</v>
       </c>
       <c r="W111" s="4"/>
       <c r="X111" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y111" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z111" s="4"/>
-      <c r="AA111" s="16"/>
-      <c r="AB111" s="16"/>
+      <c r="AA111" s="12"/>
+      <c r="AB111" s="12"/>
       <c r="AC111" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>22.442947653318569</v>
       </c>
       <c r="AD111" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>22.442947653318569</v>
       </c>
       <c r="AE111" s="12">
@@ -19829,14 +20137,17 @@
         <v>110</v>
       </c>
       <c r="AP111" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ111" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR111" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR111" s="12">
+        <f t="shared" si="39"/>
+        <v>19.508400000000002</v>
+      </c>
       <c r="AS111" s="12"/>
       <c r="AT111" s="12"/>
       <c r="AU111" s="12"/>
@@ -19871,7 +20182,7 @@
         <v>20</v>
       </c>
       <c r="L112" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-20</v>
       </c>
       <c r="M112" s="12"/>
@@ -19886,27 +20197,27 @@
       <c r="T112" s="12"/>
       <c r="U112" s="12"/>
       <c r="V112" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="W112" s="4"/>
       <c r="X112" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y112" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z112" s="4"/>
-      <c r="AA112" s="16"/>
-      <c r="AB112" s="16"/>
+      <c r="AA112" s="12"/>
+      <c r="AB112" s="12"/>
       <c r="AC112" s="12" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD112" s="12" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE112" s="12">
@@ -19943,14 +20254,17 @@
         <v>110</v>
       </c>
       <c r="AP112" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ112" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR112" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR112" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS112" s="12"/>
       <c r="AT112" s="12"/>
       <c r="AU112" s="12"/>
@@ -19987,7 +20301,7 @@
         <v>109</v>
       </c>
       <c r="L113" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-8</v>
       </c>
       <c r="M113" s="12"/>
@@ -20002,7 +20316,7 @@
       <c r="T113" s="12"/>
       <c r="U113" s="12"/>
       <c r="V113" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>20.2</v>
       </c>
       <c r="W113" s="4">
@@ -20010,22 +20324,22 @@
         <v>120.29999999999998</v>
       </c>
       <c r="X113" s="4">
-        <f t="shared" si="33"/>
-        <v>120.29999999999998</v>
-      </c>
-      <c r="Y113" s="4">
         <f t="shared" si="34"/>
         <v>120.29999999999998</v>
       </c>
+      <c r="Y113" s="4">
+        <f t="shared" si="35"/>
+        <v>120.29999999999998</v>
+      </c>
       <c r="Z113" s="4"/>
-      <c r="AA113" s="16"/>
-      <c r="AB113" s="16"/>
+      <c r="AA113" s="12"/>
+      <c r="AB113" s="12"/>
       <c r="AC113" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>7.9999999999999982</v>
       </c>
       <c r="AD113" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2.0445544554455446</v>
       </c>
       <c r="AE113" s="12">
@@ -20060,14 +20374,17 @@
       </c>
       <c r="AO113" s="12"/>
       <c r="AP113" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>11</v>
       </c>
       <c r="AQ113" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR113" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR113" s="12">
+        <f t="shared" si="39"/>
+        <v>1.8179999999999998</v>
+      </c>
       <c r="AS113" s="12"/>
       <c r="AT113" s="12"/>
       <c r="AU113" s="12"/>
@@ -20094,7 +20411,7 @@
       <c r="J114" s="8"/>
       <c r="K114" s="8"/>
       <c r="L114" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M114" s="8"/>
@@ -20109,27 +20426,27 @@
       <c r="T114" s="8"/>
       <c r="U114" s="8"/>
       <c r="V114" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="W114" s="10"/>
       <c r="X114" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y114" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z114" s="4"/>
-      <c r="AA114" s="16"/>
-      <c r="AB114" s="16"/>
+      <c r="AA114" s="12"/>
+      <c r="AB114" s="12"/>
       <c r="AC114" s="12" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD114" s="8" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE114" s="8">
@@ -20166,14 +20483,17 @@
         <v>46</v>
       </c>
       <c r="AP114" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ114" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR114" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR114" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS114" s="12"/>
       <c r="AT114" s="12"/>
       <c r="AU114" s="12"/>
@@ -20212,7 +20532,7 @@
         <v>487.3</v>
       </c>
       <c r="L115" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>12.313999999999965</v>
       </c>
       <c r="M115" s="12"/>
@@ -20231,7 +20551,7 @@
         <v>214.2</v>
       </c>
       <c r="V115" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>99.922799999999995</v>
       </c>
       <c r="W115" s="4">
@@ -20239,25 +20559,25 @@
         <v>275.47713679999993</v>
       </c>
       <c r="X115" s="4">
-        <f t="shared" ref="X115:X118" si="51">W115+V115*$X$1</f>
+        <f t="shared" ref="X115:X118" si="53">W115+V115*$X$1</f>
         <v>461.83315879999992</v>
       </c>
       <c r="Y115" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>260.0120684044</v>
       </c>
       <c r="Z115" s="4">
-        <f t="shared" ref="Z115:Z116" si="52">X115*$Z$1</f>
+        <f t="shared" ref="Z115:Z116" si="54">X115*$Z$1</f>
         <v>201.82109039559995</v>
       </c>
-      <c r="AA115" s="16"/>
-      <c r="AB115" s="16"/>
+      <c r="AA115" s="12"/>
+      <c r="AB115" s="12"/>
       <c r="AC115" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.864999999999998</v>
       </c>
       <c r="AD115" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>8.2431003054357959</v>
       </c>
       <c r="AE115" s="12">
@@ -20292,14 +20612,17 @@
       </c>
       <c r="AO115" s="12"/>
       <c r="AP115" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>260</v>
       </c>
       <c r="AQ115" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>202</v>
       </c>
-      <c r="AR115" s="12"/>
+      <c r="AR115" s="12">
+        <f t="shared" si="39"/>
+        <v>99.922799999999995</v>
+      </c>
       <c r="AS115" s="12"/>
       <c r="AT115" s="12"/>
       <c r="AU115" s="12"/>
@@ -20338,7 +20661,7 @@
         <v>615.57299999999998</v>
       </c>
       <c r="L116" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>19.212999999999965</v>
       </c>
       <c r="M116" s="12"/>
@@ -20357,7 +20680,7 @@
         <v>275.39999999999998</v>
       </c>
       <c r="V116" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>126.95719999999999</v>
       </c>
       <c r="W116" s="4">
@@ -20365,25 +20688,25 @@
         <v>337.84534399999984</v>
       </c>
       <c r="X116" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>574.62052199999982</v>
       </c>
       <c r="Y116" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>323.51135388599994</v>
       </c>
       <c r="Z116" s="4">
+        <f t="shared" si="54"/>
+        <v>251.10916811399991</v>
+      </c>
+      <c r="AA116" s="12"/>
+      <c r="AB116" s="12"/>
+      <c r="AC116" s="12">
+        <f t="shared" si="36"/>
+        <v>12.865000000000002</v>
+      </c>
+      <c r="AD116" s="12">
         <f t="shared" si="52"/>
-        <v>251.10916811399991</v>
-      </c>
-      <c r="AA116" s="16"/>
-      <c r="AB116" s="16"/>
-      <c r="AC116" s="12">
-        <f t="shared" si="35"/>
-        <v>12.865000000000002</v>
-      </c>
-      <c r="AD116" s="12">
-        <f t="shared" si="50"/>
         <v>8.3389036305148529</v>
       </c>
       <c r="AE116" s="12">
@@ -20418,14 +20741,17 @@
       </c>
       <c r="AO116" s="12"/>
       <c r="AP116" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>324</v>
       </c>
       <c r="AQ116" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>251</v>
       </c>
-      <c r="AR116" s="12"/>
+      <c r="AR116" s="12">
+        <f t="shared" si="39"/>
+        <v>126.95719999999999</v>
+      </c>
       <c r="AS116" s="12"/>
       <c r="AT116" s="12"/>
       <c r="AU116" s="12"/>
@@ -20464,7 +20790,7 @@
         <v>238.15</v>
       </c>
       <c r="L117" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>6.1080000000000041</v>
       </c>
       <c r="M117" s="12"/>
@@ -20481,7 +20807,7 @@
         <v>171.36</v>
       </c>
       <c r="V117" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>48.851600000000005</v>
       </c>
       <c r="W117" s="4">
@@ -20489,22 +20815,22 @@
         <v>100.35160000000005</v>
       </c>
       <c r="X117" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>191.45983400000006</v>
       </c>
       <c r="Y117" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>191.45983400000006</v>
       </c>
       <c r="Z117" s="4"/>
-      <c r="AA117" s="16"/>
-      <c r="AB117" s="16"/>
+      <c r="AA117" s="12"/>
+      <c r="AB117" s="12"/>
       <c r="AC117" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.865</v>
       </c>
       <c r="AD117" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>8.945786831956374</v>
       </c>
       <c r="AE117" s="12">
@@ -20539,14 +20865,17 @@
       </c>
       <c r="AO117" s="12"/>
       <c r="AP117" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>191</v>
       </c>
       <c r="AQ117" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR117" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR117" s="12">
+        <f t="shared" si="39"/>
+        <v>48.851600000000005</v>
+      </c>
       <c r="AS117" s="12"/>
       <c r="AT117" s="12"/>
       <c r="AU117" s="12"/>
@@ -20585,7 +20914,7 @@
         <v>1813.2</v>
       </c>
       <c r="L118" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-41.527000000000044</v>
       </c>
       <c r="M118" s="12"/>
@@ -20606,7 +20935,7 @@
         <v>887.4</v>
       </c>
       <c r="V118" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>354.33460000000002</v>
       </c>
       <c r="W118" s="4">
@@ -20614,25 +20943,25 @@
         <v>520.92165966920015</v>
       </c>
       <c r="X118" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1181.7556886692</v>
       </c>
       <c r="Y118" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>665.32845272075963</v>
       </c>
       <c r="Z118" s="4">
         <f>X118*$Z$1</f>
         <v>516.4272359484404</v>
       </c>
-      <c r="AA118" s="16"/>
-      <c r="AB118" s="16"/>
+      <c r="AA118" s="12"/>
+      <c r="AB118" s="12"/>
       <c r="AC118" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.865</v>
       </c>
       <c r="AD118" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>9.5298594614547945</v>
       </c>
       <c r="AE118" s="12">
@@ -20667,14 +20996,17 @@
       </c>
       <c r="AO118" s="12"/>
       <c r="AP118" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>665</v>
       </c>
       <c r="AQ118" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>516</v>
       </c>
-      <c r="AR118" s="12"/>
+      <c r="AR118" s="12">
+        <f t="shared" si="39"/>
+        <v>354.33460000000002</v>
+      </c>
       <c r="AS118" s="12"/>
       <c r="AT118" s="12"/>
       <c r="AU118" s="12"/>
@@ -20711,7 +21043,7 @@
         <v>74</v>
       </c>
       <c r="L119" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>2</v>
       </c>
       <c r="M119" s="12"/>
@@ -20726,27 +21058,27 @@
       <c r="T119" s="12"/>
       <c r="U119" s="12"/>
       <c r="V119" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>15.2</v>
       </c>
       <c r="W119" s="4"/>
       <c r="X119" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y119" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z119" s="4"/>
-      <c r="AA119" s="16"/>
-      <c r="AB119" s="16"/>
+      <c r="AA119" s="12"/>
+      <c r="AB119" s="12"/>
       <c r="AC119" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>19.736842105263158</v>
       </c>
       <c r="AD119" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>19.736842105263158</v>
       </c>
       <c r="AE119" s="12">
@@ -20781,14 +21113,17 @@
       </c>
       <c r="AO119" s="12"/>
       <c r="AP119" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ119" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR119" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR119" s="12">
+        <f t="shared" si="39"/>
+        <v>3.8</v>
+      </c>
       <c r="AS119" s="12"/>
       <c r="AT119" s="12"/>
       <c r="AU119" s="12"/>
@@ -20827,7 +21162,7 @@
         <v>41</v>
       </c>
       <c r="L120" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M120" s="12"/>
@@ -20842,27 +21177,27 @@
       <c r="T120" s="12"/>
       <c r="U120" s="12"/>
       <c r="V120" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="W120" s="4"/>
       <c r="X120" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y120" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z120" s="4"/>
-      <c r="AA120" s="16"/>
-      <c r="AB120" s="16"/>
+      <c r="AA120" s="12"/>
+      <c r="AB120" s="12"/>
       <c r="AC120" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>44.512195121951223</v>
       </c>
       <c r="AD120" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>44.512195121951223</v>
       </c>
       <c r="AE120" s="12">
@@ -20899,14 +21234,17 @@
         <v>110</v>
       </c>
       <c r="AP120" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ120" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR120" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR120" s="12">
+        <f t="shared" si="39"/>
+        <v>2.665</v>
+      </c>
       <c r="AS120" s="12"/>
       <c r="AT120" s="12"/>
       <c r="AU120" s="12"/>
@@ -20945,7 +21283,7 @@
         <v>56</v>
       </c>
       <c r="L121" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M121" s="12"/>
@@ -20960,27 +21298,27 @@
       <c r="T121" s="12"/>
       <c r="U121" s="12"/>
       <c r="V121" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>11.2</v>
       </c>
       <c r="W121" s="4"/>
       <c r="X121" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y121" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z121" s="4"/>
-      <c r="AA121" s="16"/>
-      <c r="AB121" s="16"/>
+      <c r="AA121" s="12"/>
+      <c r="AB121" s="12"/>
       <c r="AC121" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>15.803571428571429</v>
       </c>
       <c r="AD121" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>15.803571428571429</v>
       </c>
       <c r="AE121" s="12">
@@ -21017,14 +21355,17 @@
         <v>167</v>
       </c>
       <c r="AP121" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ121" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR121" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR121" s="12">
+        <f t="shared" si="39"/>
+        <v>2.8</v>
+      </c>
       <c r="AS121" s="12"/>
       <c r="AT121" s="12"/>
       <c r="AU121" s="12"/>
@@ -21059,7 +21400,7 @@
         <v>2.7</v>
       </c>
       <c r="L122" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-1.33</v>
       </c>
       <c r="M122" s="8"/>
@@ -21074,27 +21415,27 @@
       <c r="T122" s="8"/>
       <c r="U122" s="8"/>
       <c r="V122" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.27400000000000002</v>
       </c>
       <c r="W122" s="10"/>
       <c r="X122" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y122" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z122" s="4"/>
-      <c r="AA122" s="16"/>
-      <c r="AB122" s="16"/>
+      <c r="AA122" s="12"/>
+      <c r="AB122" s="12"/>
       <c r="AC122" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>348.32116788321167</v>
       </c>
       <c r="AD122" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>348.32116788321167</v>
       </c>
       <c r="AE122" s="8">
@@ -21131,14 +21472,17 @@
         <v>170</v>
       </c>
       <c r="AP122" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ122" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR122" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR122" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS122" s="12"/>
       <c r="AT122" s="12"/>
       <c r="AU122" s="12"/>
@@ -21173,7 +21517,7 @@
         <v>145</v>
       </c>
       <c r="L123" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-114</v>
       </c>
       <c r="M123" s="12"/>
@@ -21190,29 +21534,29 @@
         <v>100</v>
       </c>
       <c r="V123" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>6.2</v>
       </c>
       <c r="W123" s="4">
         <v>50</v>
       </c>
       <c r="X123" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>50</v>
       </c>
       <c r="Y123" s="4">
-        <f t="shared" ref="Y123:Y124" si="53">X123</f>
+        <f t="shared" ref="Y123:Y124" si="55">X123</f>
         <v>50</v>
       </c>
       <c r="Z123" s="4"/>
-      <c r="AA123" s="16"/>
-      <c r="AB123" s="16"/>
+      <c r="AA123" s="12"/>
+      <c r="AB123" s="12"/>
       <c r="AC123" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>40.322580645161288</v>
       </c>
       <c r="AD123" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>32.258064516129032</v>
       </c>
       <c r="AE123" s="12">
@@ -21247,14 +21591,17 @@
       </c>
       <c r="AO123" s="12"/>
       <c r="AP123" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>15</v>
       </c>
       <c r="AQ123" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR123" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR123" s="12">
+        <f t="shared" si="39"/>
+        <v>1.8599999999999999</v>
+      </c>
       <c r="AS123" s="12"/>
       <c r="AT123" s="12"/>
       <c r="AU123" s="12"/>
@@ -21287,7 +21634,7 @@
         <v>10</v>
       </c>
       <c r="L124" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-24</v>
       </c>
       <c r="M124" s="12"/>
@@ -21306,29 +21653,29 @@
         <v>20</v>
       </c>
       <c r="V124" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-2.8</v>
       </c>
       <c r="W124" s="4">
         <v>50</v>
       </c>
       <c r="X124" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>50</v>
       </c>
       <c r="Y124" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>50</v>
       </c>
       <c r="Z124" s="4"/>
-      <c r="AA124" s="16"/>
-      <c r="AB124" s="16"/>
+      <c r="AA124" s="12"/>
+      <c r="AB124" s="12"/>
       <c r="AC124" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-24.285714285714288</v>
       </c>
       <c r="AD124" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>-6.4285714285714288</v>
       </c>
       <c r="AE124" s="12">
@@ -21363,14 +21710,17 @@
       </c>
       <c r="AO124" s="12"/>
       <c r="AP124" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>15</v>
       </c>
       <c r="AQ124" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR124" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR124" s="12">
+        <f t="shared" si="39"/>
+        <v>-0.84</v>
+      </c>
       <c r="AS124" s="12"/>
       <c r="AT124" s="12"/>
       <c r="AU124" s="12"/>
@@ -21409,7 +21759,7 @@
         <v>259.8</v>
       </c>
       <c r="L125" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>4.728999999999985</v>
       </c>
       <c r="M125" s="12"/>
@@ -21424,7 +21774,7 @@
       <c r="T125" s="12"/>
       <c r="U125" s="12"/>
       <c r="V125" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>52.905799999999999</v>
       </c>
       <c r="W125" s="4">
@@ -21436,18 +21786,18 @@
         <v>187.68081700000005</v>
       </c>
       <c r="Y125" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>187.68081700000005</v>
       </c>
       <c r="Z125" s="4"/>
-      <c r="AA125" s="16"/>
-      <c r="AB125" s="16"/>
+      <c r="AA125" s="12"/>
+      <c r="AB125" s="12"/>
       <c r="AC125" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.865</v>
       </c>
       <c r="AD125" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>9.3175474144611723</v>
       </c>
       <c r="AE125" s="12">
@@ -21482,14 +21832,17 @@
       </c>
       <c r="AO125" s="12"/>
       <c r="AP125" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>188</v>
       </c>
       <c r="AQ125" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR125" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR125" s="12">
+        <f t="shared" si="39"/>
+        <v>52.905799999999999</v>
+      </c>
       <c r="AS125" s="12"/>
       <c r="AT125" s="12"/>
       <c r="AU125" s="12"/>
@@ -21526,7 +21879,7 @@
         <v>42</v>
       </c>
       <c r="L126" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-47</v>
       </c>
       <c r="M126" s="12"/>
@@ -21545,29 +21898,29 @@
         <v>100</v>
       </c>
       <c r="V126" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1</v>
       </c>
       <c r="W126" s="4">
         <v>100</v>
       </c>
       <c r="X126" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>100</v>
       </c>
       <c r="Y126" s="4">
-        <f t="shared" ref="Y126:Y127" si="54">X126</f>
+        <f t="shared" ref="Y126:Y127" si="56">X126</f>
         <v>100</v>
       </c>
       <c r="Z126" s="4"/>
-      <c r="AA126" s="16"/>
-      <c r="AB126" s="16"/>
+      <c r="AA126" s="12"/>
+      <c r="AB126" s="12"/>
       <c r="AC126" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-199</v>
       </c>
       <c r="AD126" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>-99</v>
       </c>
       <c r="AE126" s="12">
@@ -21602,14 +21955,17 @@
       </c>
       <c r="AO126" s="12"/>
       <c r="AP126" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>30</v>
       </c>
       <c r="AQ126" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR126" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR126" s="12">
+        <f t="shared" si="39"/>
+        <v>-0.3</v>
+      </c>
       <c r="AS126" s="12"/>
       <c r="AT126" s="12"/>
       <c r="AU126" s="12"/>
@@ -21648,7 +22004,7 @@
         <v>58</v>
       </c>
       <c r="L127" s="12">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-10</v>
       </c>
       <c r="M127" s="12"/>
@@ -21665,29 +22021,29 @@
         <v>40</v>
       </c>
       <c r="V127" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>9.6</v>
       </c>
       <c r="W127" s="4">
         <v>20</v>
       </c>
       <c r="X127" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="Y127" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>20</v>
       </c>
       <c r="Z127" s="4"/>
-      <c r="AA127" s="16"/>
-      <c r="AB127" s="16"/>
+      <c r="AA127" s="12"/>
+      <c r="AB127" s="12"/>
       <c r="AC127" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>15.9375</v>
       </c>
       <c r="AD127" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>13.854166666666668</v>
       </c>
       <c r="AE127" s="12">
@@ -21722,14 +22078,17 @@
       </c>
       <c r="AO127" s="12"/>
       <c r="AP127" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2</v>
       </c>
       <c r="AQ127" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR127" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR127" s="12">
+        <f t="shared" si="39"/>
+        <v>1.1519999999999999</v>
+      </c>
       <c r="AS127" s="12"/>
       <c r="AT127" s="12"/>
       <c r="AU127" s="12"/>
@@ -21748,10 +22107,10 @@
       <c r="D128" s="8">
         <v>100</v>
       </c>
-      <c r="E128" s="15">
+      <c r="E128" s="14">
         <v>143</v>
       </c>
-      <c r="F128" s="15">
+      <c r="F128" s="14">
         <v>52</v>
       </c>
       <c r="G128" s="9">
@@ -21768,7 +22127,7 @@
         <v>147</v>
       </c>
       <c r="L128" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-4</v>
       </c>
       <c r="M128" s="8"/>
@@ -21783,27 +22142,27 @@
       <c r="T128" s="8"/>
       <c r="U128" s="8"/>
       <c r="V128" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>28.6</v>
       </c>
       <c r="W128" s="10"/>
       <c r="X128" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y128" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z128" s="4"/>
-      <c r="AA128" s="16"/>
-      <c r="AB128" s="16"/>
+      <c r="AA128" s="12"/>
+      <c r="AB128" s="12"/>
       <c r="AC128" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.8181818181818181</v>
       </c>
       <c r="AD128" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>1.8181818181818181</v>
       </c>
       <c r="AE128" s="8">
@@ -21838,14 +22197,17 @@
       </c>
       <c r="AO128" s="8"/>
       <c r="AP128" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ128" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR128" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR128" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS128" s="12"/>
       <c r="AT128" s="12"/>
       <c r="AU128" s="12"/>
@@ -21878,7 +22240,7 @@
         <v>1</v>
       </c>
       <c r="L129" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>-1</v>
       </c>
       <c r="M129" s="8"/>
@@ -21893,27 +22255,27 @@
       <c r="T129" s="8"/>
       <c r="U129" s="8"/>
       <c r="V129" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="W129" s="10"/>
       <c r="X129" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Y129" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z129" s="4"/>
-      <c r="AA129" s="16"/>
-      <c r="AB129" s="16"/>
+      <c r="AA129" s="12"/>
+      <c r="AB129" s="12"/>
       <c r="AC129" s="12" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD129" s="8" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE129" s="8">
@@ -21948,14 +22310,17 @@
       </c>
       <c r="AO129" s="8"/>
       <c r="AP129" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AQ129" s="12">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="AR129" s="12"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AR129" s="12">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AS129" s="12"/>
       <c r="AT129" s="12"/>
       <c r="AU129" s="12"/>
